--- a/top_n_otc.xlsx
+++ b/top_n_otc.xlsx
@@ -969,7 +969,7 @@
         <v>0.2824096008554864</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.2924482618098654</v>
+        <v>0.2926315239180217</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>1.163700926871588</v>
@@ -1989,26 +1989,26 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>GLPGF</t>
+          <t>NXCLF</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Lakefront Biotherapeutics</t>
+          <t>LIFULL Co., Ltd.</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="F29" s="10" t="n">
-        <v>3189103616</v>
+        <v>202778128</v>
       </c>
       <c r="G29" s="17" t="inlineStr">
         <is>
@@ -2016,46 +2016,48 @@
         </is>
       </c>
       <c r="H29" s="18" t="n">
-        <v>0.881989217820347</v>
+        <v>0.8938697664316019</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>0.5877493536277286</v>
+        <v>0.5358060628784111</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>0.5358009711298616</v>
+        <v>0.2390220859642449</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>4.6826925</v>
+        <v>9.875000999999999</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>0.9802465124613901</v>
-      </c>
-      <c r="M29" s="20" t="n">
-        <v>-9.730978900874939</v>
+        <v>0.0074367597462133</v>
+      </c>
+      <c r="M29" s="24" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N29" s="20" t="n">
-        <v>214.8679223530429</v>
+        <v>14.40111736061304</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>-7.475150278954917</v>
+        <v>0.200456447318372</v>
       </c>
       <c r="P29" s="20" t="n">
-        <v>38.14057362285293</v>
+        <v>18.69378177551818</v>
       </c>
       <c r="Q29" s="20" t="n">
-        <v>-8.347884944836451</v>
+        <v>31.55704209289034</v>
       </c>
       <c r="R29" s="21" t="n">
-        <v>0.6458697123620912</v>
+        <v>0.5131200055934176</v>
       </c>
       <c r="S29" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T29" s="21" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="U29" s="21" t="n">
-        <v>3.055422759429443</v>
+        <v>0.0072093763287943</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -2064,17 +2066,17 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>VTSYF</t>
+          <t>GLPGF</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Vitasoy International Holdings Limited</t>
+          <t>Lakefront Biotherapeutics</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -2083,7 +2085,7 @@
         </is>
       </c>
       <c r="F30" s="10" t="n">
-        <v>803658432</v>
+        <v>3189103616</v>
       </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
@@ -2091,46 +2093,46 @@
         </is>
       </c>
       <c r="H30" s="18" t="n">
-        <v>0.8808517979838447</v>
+        <v>0.881989217820347</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0.5111983023788198</v>
+        <v>0.5877493536277286</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>0.2022806204753344</v>
+        <v>0.5358009711298616</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>26.333334</v>
+        <v>4.6826925</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>0.277008686396643</v>
+        <v>0.9802465124613901</v>
       </c>
       <c r="M30" s="20" t="n">
-        <v>69.75052804522805</v>
+        <v>-9.730978900874939</v>
       </c>
       <c r="N30" s="20" t="n">
-        <v>14.19375766373652</v>
+        <v>214.8679223530429</v>
       </c>
       <c r="O30" s="19" t="n">
-        <v>-0.7997894533258902</v>
+        <v>-7.475150278954917</v>
       </c>
       <c r="P30" s="20" t="n">
-        <v>15.01383812161213</v>
+        <v>38.14057362285293</v>
       </c>
       <c r="Q30" s="20" t="n">
-        <v>-30.5390929037204</v>
+        <v>-8.347884944836451</v>
       </c>
       <c r="R30" s="21" t="n">
-        <v>0.9897038473558776</v>
+        <v>0.6458697123620912</v>
       </c>
       <c r="S30" s="22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T30" s="21" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="U30" s="21" t="n">
-        <v>0.1325916317929503</v>
+        <v>3.055422759429443</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -2139,26 +2141,26 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>AKRTF</t>
+          <t>VTSYF</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Aker Solutions ASA</t>
+          <t>Vitasoy International Holdings Limited</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2162934272</v>
+        <v>803658432</v>
       </c>
       <c r="G31" s="17" t="inlineStr">
         <is>
@@ -2166,46 +2168,46 @@
         </is>
       </c>
       <c r="H31" s="18" t="n">
-        <v>0.8756363829574741</v>
+        <v>0.8808517979838447</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>0.5740475914015073</v>
+        <v>0.5111983023788198</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>0.1002714467046379</v>
+        <v>0.2022806204753344</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>6.357143</v>
+        <v>26.333334</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>0.1899476834987266</v>
+        <v>0.277008686396643</v>
       </c>
       <c r="M31" s="20" t="n">
-        <v>97.83006480559388</v>
+        <v>69.75052804522805</v>
       </c>
       <c r="N31" s="20" t="n">
-        <v>29.09419471425344</v>
+        <v>14.19375766373652</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>-0.5152563059397884</v>
+        <v>-0.7997894533258902</v>
       </c>
       <c r="P31" s="20" t="n">
-        <v>7.903282852641389</v>
+        <v>15.01383812161213</v>
       </c>
       <c r="Q31" s="20" t="n">
-        <v>48.68024603713753</v>
+        <v>-30.5390929037204</v>
       </c>
       <c r="R31" s="21" t="n">
-        <v>0.6682729016026684</v>
+        <v>0.9897038473558776</v>
       </c>
       <c r="S31" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T31" s="21" t="n">
         <v>1</v>
       </c>
       <c r="U31" s="21" t="n">
-        <v>0.0347727447992026</v>
+        <v>0.1325916317929503</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -2214,17 +2216,17 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>NXCLF</t>
+          <t>AKRTF</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>LIFULL Co., Ltd.</t>
+          <t>Aker Solutions ASA</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -2233,7 +2235,7 @@
         </is>
       </c>
       <c r="F32" s="10" t="n">
-        <v>202778128</v>
+        <v>2162934272</v>
       </c>
       <c r="G32" s="17" t="inlineStr">
         <is>
@@ -2241,48 +2243,46 @@
         </is>
       </c>
       <c r="H32" s="18" t="n">
-        <v>0.8752474796309435</v>
+        <v>0.8756363829574741</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>0.5358060628784111</v>
+        <v>0.5740475914015073</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>0.2390220859642449</v>
+        <v>0.1002714467046379</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>9.875000999999999</v>
+        <v>6.357143</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>0.0074367597462133</v>
-      </c>
-      <c r="M32" s="24" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.1899476834987266</v>
+      </c>
+      <c r="M32" s="20" t="n">
+        <v>97.83006480559388</v>
       </c>
       <c r="N32" s="20" t="n">
-        <v>14.40111736061304</v>
+        <v>29.09419471425344</v>
       </c>
       <c r="O32" s="19" t="n">
-        <v>0.200456447318372</v>
+        <v>-0.5152563059397884</v>
       </c>
       <c r="P32" s="20" t="n">
-        <v>18.69378177551818</v>
+        <v>7.903282852641389</v>
       </c>
       <c r="Q32" s="20" t="n">
-        <v>31.55704209289034</v>
+        <v>48.68024603713753</v>
       </c>
       <c r="R32" s="21" t="n">
-        <v>0.5131200055934176</v>
+        <v>0.6682729016026684</v>
       </c>
       <c r="S32" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T32" s="21" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="U32" s="21" t="n">
-        <v>0.0072093763287943</v>
+        <v>0.0347727447992026</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -2780,7 +2780,7 @@
         </is>
       </c>
       <c r="H39" s="18" t="n">
-        <v>0.8484462743863785</v>
+        <v>0.8425071504656739</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>0.4713590413257659</v>
@@ -2818,7 +2818,7 @@
         <v>3</v>
       </c>
       <c r="T39" s="21" t="n">
-        <v>0.875</v>
+        <v>0.833</v>
       </c>
       <c r="U39" s="21" t="n">
         <v>0.0112918851891152</v>

--- a/top_n_otc.xlsx
+++ b/top_n_otc.xlsx
@@ -26,14 +26,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UK" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SG" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AU" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SE" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DE" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NL" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NO" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GR" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GR" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SE" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DE" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NL" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NO" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IT" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IS" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AR" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AR" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IS" sheetId="27" state="visible" r:id="rId27"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TH" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames>
@@ -55,14 +55,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'UK'!$A$16:$V$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'SG'!$A$16:$V$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'AU'!$A$16:$V$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'SE'!$A$16:$V$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'DE'!$A$16:$V$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'NL'!$A$16:$V$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'NO'!$A$16:$V$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'GR'!$A$16:$V$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'GR'!$A$16:$V$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'SE'!$A$16:$V$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'DE'!$A$16:$V$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'NL'!$A$16:$V$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'NO'!$A$16:$V$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'IT'!$A$16:$V$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'IS'!$A$16:$V$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'AR'!$A$16:$V$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'AR'!$A$16:$V$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'IS'!$A$16:$V$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'TH'!$A$16:$V$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="H23" s="12" t="n">
-        <v>0.7746323141100037</v>
+        <v>0.7852735723144277</v>
       </c>
     </row>
     <row r="24">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="H25" s="12" t="n">
-        <v>0.6472407538639148</v>
+        <v>0.6544985162921796</v>
       </c>
     </row>
     <row r="26">
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="H28" s="12" t="n">
-        <v>0.4996922565604084</v>
+        <v>0.5084812738982244</v>
       </c>
     </row>
     <row r="29">
@@ -1298,51 +1298,51 @@
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>BTRYF</t>
+          <t>CKDXF</t>
         </is>
       </c>
       <c r="H35" s="12" t="n">
-        <v>0.2584026939874546</v>
+        <v>0.2826354242812499</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>EVGGF</t>
+          <t>ATEK</t>
         </is>
       </c>
       <c r="H36" s="12" t="n">
-        <v>0.2554027856643192</v>
+        <v>0.2604063576671203</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
@@ -1356,51 +1356,51 @@
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>TELDF</t>
+          <t>EVGGF</t>
         </is>
       </c>
       <c r="H37" s="12" t="n">
-        <v>0.2134926875407663</v>
+        <v>0.2554027856643192</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
-          <t>ICTSF</t>
+          <t>TELDF</t>
         </is>
       </c>
       <c r="H38" s="12" t="n">
-        <v>0.1929802370832626</v>
+        <v>0.2134926875407663</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>TGSGY</t>
+          <t>ICTSF</t>
         </is>
       </c>
       <c r="H39" s="12" t="n">
-        <v>0.1843209443780383</v>
+        <v>0.1929802370832626</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
-          <t>ATEK</t>
+          <t>TGSGY</t>
         </is>
       </c>
       <c r="H40" s="12" t="n">
-        <v>0.1841351013705103</v>
+        <v>0.1843209443780383</v>
       </c>
     </row>
     <row r="41">
@@ -1482,59 +1482,59 @@
     <row r="42">
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>OSSFF</t>
+          <t>HGLD</t>
         </is>
       </c>
       <c r="H42" s="12" t="n">
-        <v>0.1217736937364642</v>
+        <v>0.171834096526976</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="D43" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>HGLD</t>
+          <t>OSSFF</t>
         </is>
       </c>
       <c r="H43" s="12" t="n">
-        <v>0.1215050548932885</v>
+        <v>0.1217736937364642</v>
       </c>
     </row>
     <row r="44">
@@ -2742,10 +2742,10 @@
         <v>0.4121282296961923</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.4996922565604084</v>
+        <v>0.5084812738982244</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>0.4996922565604084</v>
+        <v>0.5084812738982244</v>
       </c>
     </row>
     <row r="12">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="H18" s="18" t="n">
-        <v>0.4996922565604084</v>
+        <v>0.5084812738982244</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>0.4121282296961923</v>
@@ -3008,7 +3008,7 @@
         <v>1</v>
       </c>
       <c r="U18" s="21" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="V18" s="12" t="n">
         <v>0.0009446001131678</v>
@@ -4315,10 +4315,10 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="13" t="n">
-        <v>0.2263563328282867</v>
+        <v>0.246748234465382</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.2124342588997609</v>
+        <v>0.2293708697246789</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>0.4732104658810096</v>
@@ -4654,10 +4654,8 @@
       <c r="O19" s="19" t="n">
         <v>-30.3608903466146</v>
       </c>
-      <c r="P19" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P19" s="12" t="n">
+        <v>5.929292369121562</v>
       </c>
       <c r="Q19" s="19" t="n">
         <v>-196.087386770191</v>
@@ -4764,26 +4762,26 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>NWHUF</t>
+          <t>DGTHF</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>NorthWest Healthcare Properties Real Estate Invest</t>
+          <t>DGTL Holdings Inc.</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="F21" s="10" t="n">
-        <v>997524864</v>
+        <v>14369180</v>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
@@ -4791,24 +4789,26 @@
         </is>
       </c>
       <c r="H21" s="18" t="n">
-        <v>0.3128662824427244</v>
+        <v>0.3179254999357841</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>0.3048351494179065</v>
+        <v>0.3320947992537183</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>14.74464263035703</v>
+        <v>-0.3885321071389489</v>
       </c>
       <c r="K21" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L21" s="12" t="n">
-        <v>0.6501676145732986</v>
+      <c r="L21" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M21" s="19" t="n">
-        <v>12.79847797357761</v>
+        <v>-1.34640250870265</v>
       </c>
       <c r="N21" s="20" t="inlineStr">
         <is>
@@ -4816,28 +4816,30 @@
         </is>
       </c>
       <c r="O21" s="19" t="n">
-        <v>8.374807887928171</v>
+        <v>95.35236191443693</v>
       </c>
       <c r="P21" s="12" t="n">
-        <v>8.468450774926271</v>
+        <v>0.0284734008655742</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>41.40071958331709</v>
+        <v>0</v>
       </c>
       <c r="R21" s="19" t="n">
-        <v>13.36038409620495</v>
+        <v>-66.66666896622851</v>
       </c>
       <c r="S21" s="21" t="n">
-        <v>0.8142656329675496</v>
+        <v>0.5808823529411764</v>
       </c>
       <c r="T21" s="15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U21" s="21" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="V21" s="12" t="n">
-        <v>2.591343864707945</v>
+        <v>0.25</v>
+      </c>
+      <c r="V21" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -4846,26 +4848,26 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>SNCAF</t>
+          <t>NWHUF</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>SNC-Lavalin Group Inc.</t>
+          <t>NorthWest Healthcare Properties Real Estate Invest</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="F22" s="10" t="n">
-        <v>10039514112</v>
+        <v>997524864</v>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
@@ -4873,22 +4875,24 @@
         </is>
       </c>
       <c r="H22" s="18" t="n">
-        <v>0.3031357953978204</v>
+        <v>0.3128662824427244</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>0.2699286012544677</v>
+        <v>0.3048351494179065</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>2.961608604405934</v>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>5.628988</v>
+        <v>14.74464263035703</v>
+      </c>
+      <c r="K22" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L22" s="12" t="n">
-        <v>1.859488147782379</v>
+        <v>0.6501676145732986</v>
       </c>
       <c r="M22" s="19" t="n">
-        <v>3.3527917411627</v>
+        <v>12.79847797357761</v>
       </c>
       <c r="N22" s="20" t="inlineStr">
         <is>
@@ -4896,28 +4900,28 @@
         </is>
       </c>
       <c r="O22" s="19" t="n">
-        <v>13.68570024459416</v>
+        <v>8.374807887928171</v>
       </c>
       <c r="P22" s="12" t="n">
-        <v>-0.0194049092468282</v>
+        <v>8.468450774926271</v>
       </c>
       <c r="Q22" s="19" t="n">
-        <v>30.49950933151842</v>
+        <v>41.40071958331709</v>
       </c>
       <c r="R22" s="19" t="n">
-        <v>-14.14312069462682</v>
+        <v>13.36038409620495</v>
       </c>
       <c r="S22" s="21" t="n">
-        <v>0.5509402966009386</v>
+        <v>0.8142656329675496</v>
       </c>
       <c r="T22" s="15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U22" s="21" t="n">
-        <v>0.85</v>
+        <v>0.625</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>0.8764474948931804</v>
+        <v>2.591343864707945</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -4926,26 +4930,26 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>RPKIF</t>
+          <t>SNCAF</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Richards Packaging Income Fund</t>
+          <t>SNC-Lavalin Group Inc.</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="F23" s="10" t="n">
-        <v>225863408</v>
+        <v>10039514112</v>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
@@ -4953,22 +4957,22 @@
         </is>
       </c>
       <c r="H23" s="18" t="n">
-        <v>0.2996785237673338</v>
+        <v>0.3031357953978204</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>0.336084923057542</v>
+        <v>0.2699286012544677</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>6.168712667433563</v>
+        <v>2.961608604405934</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>19.198114</v>
+        <v>5.628988</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>1.062556608300481</v>
+        <v>1.859488147782379</v>
       </c>
       <c r="M23" s="19" t="n">
-        <v>13.41120293376606</v>
+        <v>3.3527917411627</v>
       </c>
       <c r="N23" s="20" t="inlineStr">
         <is>
@@ -4976,28 +4980,28 @@
         </is>
       </c>
       <c r="O23" s="19" t="n">
-        <v>13.82205972363005</v>
+        <v>13.68570024459416</v>
       </c>
       <c r="P23" s="12" t="n">
-        <v>1.318742810349198</v>
+        <v>-0.0194049092468282</v>
       </c>
       <c r="Q23" s="19" t="n">
-        <v>11.99992513061198</v>
+        <v>30.49950933151842</v>
       </c>
       <c r="R23" s="19" t="n">
-        <v>-12.10424248774539</v>
+        <v>-14.14312069462682</v>
       </c>
       <c r="S23" s="21" t="n">
-        <v>0.7756841875007301</v>
+        <v>0.5509402966009386</v>
       </c>
       <c r="T23" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" s="21" t="n">
-        <v>0.778</v>
+        <v>0.85</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>0.528445472858677</v>
+        <v>0.8764474948931804</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -5006,12 +5010,12 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>SIRZF</t>
+          <t>RPKIF</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>SIR Royalty Income Fund</t>
+          <t>Richards Packaging Income Fund</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
@@ -5021,11 +5025,11 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="F24" s="10" t="n">
-        <v>95870368</v>
+        <v>225863408</v>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
@@ -5033,57 +5037,51 @@
         </is>
       </c>
       <c r="H24" s="18" t="n">
-        <v>0.279512461550133</v>
+        <v>0.2996785237673338</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>0.2866794477437261</v>
-      </c>
-      <c r="J24" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.336084923057542</v>
+      </c>
+      <c r="J24" s="12" t="n">
+        <v>6.168712667433563</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>14.729729</v>
+        <v>19.198114</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>1.127101914439973</v>
+        <v>1.062556608300481</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>11.16810983765077</v>
+        <v>13.41120293376606</v>
       </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O24" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P24" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="O24" s="19" t="n">
+        <v>13.82205972363005</v>
+      </c>
+      <c r="P24" s="12" t="n">
+        <v>1.318742810349198</v>
       </c>
       <c r="Q24" s="19" t="n">
-        <v>78.339</v>
+        <v>11.99992513061198</v>
       </c>
       <c r="R24" s="19" t="n">
-        <v>14.96686457410534</v>
+        <v>-12.10424248774539</v>
       </c>
       <c r="S24" s="21" t="n">
-        <v>0.818401690771658</v>
+        <v>0.7756841875007301</v>
       </c>
       <c r="T24" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" s="21" t="n">
-        <v>1</v>
+        <v>0.778</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>7.392124930518379</v>
+        <v>0.528445472858677</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -5092,26 +5090,26 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>CWXZF</t>
+          <t>SIRZF</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Doman Building Materials Group Ltd.</t>
+          <t>SIR Royalty Income Fund</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="F25" s="10" t="n">
-        <v>684550528</v>
+        <v>95870368</v>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
@@ -5119,51 +5117,57 @@
         </is>
       </c>
       <c r="H25" s="18" t="n">
-        <v>0.2734583998121536</v>
+        <v>0.279512461550133</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>0.3155167875991158</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>7.226030250843548</v>
+        <v>0.2866794477437261</v>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K25" s="12" t="n">
-        <v>12.000001</v>
+        <v>14.729729</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>1.02673133271739</v>
+        <v>1.127101914439973</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>19.17900792269931</v>
+        <v>11.16810983765077</v>
       </c>
       <c r="N25" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O25" s="19" t="n">
-        <v>8.391044462063579</v>
-      </c>
-      <c r="P25" s="12" t="n">
-        <v>3.987566918886905</v>
+      <c r="O25" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P25" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q25" s="19" t="n">
-        <v>8.311312664993089</v>
+        <v>78.339</v>
       </c>
       <c r="R25" s="19" t="n">
-        <v>27.82387362040345</v>
+        <v>14.96686457410534</v>
       </c>
       <c r="S25" s="21" t="n">
-        <v>0.7586504953964431</v>
+        <v>0.818401690771658</v>
       </c>
       <c r="T25" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" s="21" t="n">
-        <v>0.778</v>
+        <v>1</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>0.2216802961650358</v>
+        <v>7.392124930518379</v>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
@@ -5172,26 +5176,26 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>DGTHF</t>
+          <t>DRETF</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>DGTL Holdings Inc.</t>
+          <t>Dream Office Real Estate Investment Trust</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="F26" s="10" t="n">
-        <v>14369180</v>
+        <v>212654560</v>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
@@ -5199,26 +5203,24 @@
         </is>
       </c>
       <c r="H26" s="18" t="n">
-        <v>0.2595850836873057</v>
+        <v>0.2747965646347582</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>0.2711542681345405</v>
+        <v>0.2719728634622853</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>-0.3885321071389489</v>
+        <v>-26.38446879586794</v>
       </c>
       <c r="K26" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L26" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L26" s="12" t="n">
+        <v>0.2357372436904364</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>-1.34640250870265</v>
+        <v>12.80245295468858</v>
       </c>
       <c r="N26" s="20" t="inlineStr">
         <is>
@@ -5226,32 +5228,28 @@
         </is>
       </c>
       <c r="O26" s="19" t="n">
-        <v>95.35236191443693</v>
-      </c>
-      <c r="P26" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.14320297748952</v>
+      </c>
+      <c r="P26" s="12" t="n">
+        <v>-22.43973765862178</v>
       </c>
       <c r="Q26" s="19" t="n">
+        <v>-29.61098549241611</v>
+      </c>
+      <c r="R26" s="19" t="n">
+        <v>12.46226217490107</v>
+      </c>
+      <c r="S26" s="21" t="n">
+        <v>0.5899268591554582</v>
+      </c>
+      <c r="T26" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="R26" s="19" t="n">
-        <v>-66.66666896622851</v>
-      </c>
-      <c r="S26" s="21" t="n">
-        <v>0.5808823529411764</v>
-      </c>
-      <c r="T26" s="15" t="n">
-        <v>4</v>
-      </c>
       <c r="U26" s="21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V26" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.429</v>
+      </c>
+      <c r="V26" s="12" t="n">
+        <v>1.169929415130359</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -5260,17 +5258,17 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>EFRTF</t>
+          <t>CWXZF</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Nexus Real Estate Investment Trust</t>
+          <t>Doman Building Materials Group Ltd.</t>
         </is>
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -5279,7 +5277,7 @@
         </is>
       </c>
       <c r="F27" s="10" t="n">
-        <v>702771840</v>
+        <v>684550528</v>
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
@@ -5287,22 +5285,22 @@
         </is>
       </c>
       <c r="H27" s="18" t="n">
-        <v>0.2557992423560804</v>
+        <v>0.2734583998121536</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>0.2807805756687498</v>
+        <v>0.3155167875991158</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>17.20362873169379</v>
+        <v>7.226030250843548</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>13.714287</v>
+        <v>12.000001</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>0.636289742540408</v>
+        <v>1.02673133271739</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>6.03140273804937</v>
+        <v>19.17900792269931</v>
       </c>
       <c r="N27" s="20" t="inlineStr">
         <is>
@@ -5310,28 +5308,28 @@
         </is>
       </c>
       <c r="O27" s="19" t="n">
-        <v>5.06698548934268</v>
+        <v>8.391044462063579</v>
       </c>
       <c r="P27" s="12" t="n">
-        <v>11.6204295976883</v>
+        <v>3.987566918886905</v>
       </c>
       <c r="Q27" s="19" t="n">
-        <v>63.43366588352798</v>
+        <v>8.311312664993089</v>
       </c>
       <c r="R27" s="19" t="n">
-        <v>10.80085833177858</v>
+        <v>27.82387362040345</v>
       </c>
       <c r="S27" s="21" t="n">
-        <v>0.5138967044685014</v>
+        <v>0.7586504953964431</v>
       </c>
       <c r="T27" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U27" s="21" t="n">
-        <v>0.521</v>
+        <v>0.778</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>3.988172562906466</v>
+        <v>0.2216802961650358</v>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
@@ -5340,12 +5338,12 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>CTRRF</t>
+          <t>EFRTF</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>CT Real Estate Investment Trust</t>
+          <t>Nexus Real Estate Investment Trust</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
@@ -5355,11 +5353,11 @@
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="F28" s="10" t="n">
-        <v>3203407360</v>
+        <v>702771840</v>
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
@@ -5367,22 +5365,22 @@
         </is>
       </c>
       <c r="H28" s="18" t="n">
-        <v>0.2353105943456223</v>
+        <v>0.2557992423560804</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>0.259124099048147</v>
+        <v>0.2807805756687498</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>13.64295148500008</v>
+        <v>17.20362873169379</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>10.418605</v>
+        <v>13.714287</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>1.591694310329493</v>
+        <v>0.636289742540408</v>
       </c>
       <c r="M28" s="19" t="n">
-        <v>13.6629516890415</v>
+        <v>6.03140273804937</v>
       </c>
       <c r="N28" s="20" t="inlineStr">
         <is>
@@ -5390,28 +5388,28 @@
         </is>
       </c>
       <c r="O28" s="19" t="n">
-        <v>12.27198197315041</v>
+        <v>5.06698548934268</v>
       </c>
       <c r="P28" s="12" t="n">
-        <v>2.447042441158697</v>
+        <v>11.6204295976883</v>
       </c>
       <c r="Q28" s="19" t="n">
-        <v>105.9582119468831</v>
+        <v>63.43366588352798</v>
       </c>
       <c r="R28" s="19" t="n">
-        <v>25.89733669074787</v>
+        <v>10.80085833177858</v>
       </c>
       <c r="S28" s="21" t="n">
-        <v>0.6769155693561363</v>
+        <v>0.5138967044685014</v>
       </c>
       <c r="T28" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28" s="21" t="n">
-        <v>0.679</v>
+        <v>0.521</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>5.245871812633362</v>
+        <v>3.988172562906466</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -5420,12 +5418,12 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>DREUF</t>
+          <t>CTRRF</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Dream Industrial Real Estate Investment Trust</t>
+          <t>CT Real Estate Investment Trust</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
@@ -5435,11 +5433,11 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="F29" s="10" t="n">
-        <v>2959875328</v>
+        <v>3203407360</v>
       </c>
       <c r="G29" s="17" t="inlineStr">
         <is>
@@ -5447,22 +5445,22 @@
         </is>
       </c>
       <c r="H29" s="18" t="n">
-        <v>0.2331333729347965</v>
+        <v>0.2353105943456223</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>0.2505488606332966</v>
+        <v>0.259124099048147</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>20.61295817794733</v>
+        <v>13.64295148500008</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>22.795454</v>
+        <v>10.418605</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>0.6232896355202455</v>
+        <v>1.591694310329493</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>10.26776354818144</v>
+        <v>13.6629516890415</v>
       </c>
       <c r="N29" s="20" t="inlineStr">
         <is>
@@ -5470,28 +5468,28 @@
         </is>
       </c>
       <c r="O29" s="19" t="n">
-        <v>4.53931296884795</v>
+        <v>12.27198197315041</v>
       </c>
       <c r="P29" s="12" t="n">
-        <v>10.0929386886136</v>
+        <v>2.447042441158697</v>
       </c>
       <c r="Q29" s="19" t="n">
-        <v>55.09778721611988</v>
+        <v>105.9582119468831</v>
       </c>
       <c r="R29" s="19" t="n">
-        <v>19.05512907372221</v>
+        <v>25.89733669074787</v>
       </c>
       <c r="S29" s="21" t="n">
-        <v>0.5317528308644704</v>
+        <v>0.6769155693561363</v>
       </c>
       <c r="T29" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U29" s="21" t="n">
-        <v>0.512</v>
+        <v>0.679</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>5.825459764255756</v>
+        <v>5.245871812633362</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -5500,26 +5498,26 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>ANCTF</t>
+          <t>DREUF</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Alimentation Couche-Tard Inc.</t>
+          <t>Dream Industrial Real Estate Investment Trust</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="F30" s="10" t="n">
-        <v>59056992256</v>
+        <v>2959875328</v>
       </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
@@ -5527,22 +5525,22 @@
         </is>
       </c>
       <c r="H30" s="18" t="n">
-        <v>0.2286112953957775</v>
+        <v>0.2331333729347965</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0.2419167147045264</v>
+        <v>0.2505488606332966</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>9.020747286968906</v>
+        <v>20.61295817794733</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>19.082493</v>
+        <v>22.795454</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>3.650247684082354</v>
+        <v>0.6232896355202455</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>5.71092409410224</v>
+        <v>10.26776354818144</v>
       </c>
       <c r="N30" s="20" t="inlineStr">
         <is>
@@ -5550,28 +5548,28 @@
         </is>
       </c>
       <c r="O30" s="19" t="n">
-        <v>15.48967603646624</v>
+        <v>4.53931296884795</v>
       </c>
       <c r="P30" s="12" t="n">
-        <v>1.143226148755253</v>
+        <v>10.0929386886136</v>
       </c>
       <c r="Q30" s="19" t="n">
-        <v>9.36141457076905</v>
+        <v>55.09778721611988</v>
       </c>
       <c r="R30" s="19" t="n">
-        <v>27.14109772423025</v>
+        <v>19.05512907372221</v>
       </c>
       <c r="S30" s="21" t="n">
-        <v>0.4426420400429012</v>
+        <v>0.5317528308644704</v>
       </c>
       <c r="T30" s="15" t="n">
         <v>1</v>
       </c>
       <c r="U30" s="21" t="n">
-        <v>0.8</v>
+        <v>0.512</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>0.7719202298363801</v>
+        <v>5.825459764255756</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -5580,26 +5578,26 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>DRETF</t>
+          <t>ANCTF</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Dream Office Real Estate Investment Trust</t>
+          <t>Alimentation Couche-Tard Inc.</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="F31" s="10" t="n">
-        <v>212654560</v>
+        <v>59056992256</v>
       </c>
       <c r="G31" s="17" t="inlineStr">
         <is>
@@ -5607,24 +5605,22 @@
         </is>
       </c>
       <c r="H31" s="18" t="n">
-        <v>0.224370455474965</v>
+        <v>0.2286112953957775</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>0.2220649131220792</v>
+        <v>0.2419167147045264</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>-26.38446879586794</v>
-      </c>
-      <c r="K31" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>9.020747286968906</v>
+      </c>
+      <c r="K31" s="12" t="n">
+        <v>19.082493</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>0.2357372436904364</v>
+        <v>3.650247684082354</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>12.80245295468858</v>
+        <v>5.71092409410224</v>
       </c>
       <c r="N31" s="20" t="inlineStr">
         <is>
@@ -5632,30 +5628,28 @@
         </is>
       </c>
       <c r="O31" s="19" t="n">
-        <v>4.14320297748952</v>
-      </c>
-      <c r="P31" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>15.48967603646624</v>
+      </c>
+      <c r="P31" s="12" t="n">
+        <v>1.143226148755253</v>
       </c>
       <c r="Q31" s="19" t="n">
-        <v>-29.61098549241611</v>
+        <v>9.36141457076905</v>
       </c>
       <c r="R31" s="19" t="n">
-        <v>12.46226217490107</v>
+        <v>27.14109772423025</v>
       </c>
       <c r="S31" s="21" t="n">
-        <v>0.5899268591554582</v>
+        <v>0.4426420400429012</v>
       </c>
       <c r="T31" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U31" s="21" t="n">
-        <v>0.429</v>
+        <v>0.8</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>1.169929415130359</v>
+        <v>0.7719202298363801</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -5664,26 +5658,26 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>CNPRF</t>
+          <t>SNNGF</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Condor Petroleum Inc.</t>
+          <t>PPX Mining Corp.</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="F32" s="10" t="n">
-        <v>194044128</v>
+        <v>113023296</v>
       </c>
       <c r="G32" s="17" t="inlineStr">
         <is>
@@ -5691,24 +5685,26 @@
         </is>
       </c>
       <c r="H32" s="18" t="n">
-        <v>0.2117914394277349</v>
+        <v>0.2214883193976096</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>0.2925786992611523</v>
+        <v>0.3187031513260017</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>11.09411110572964</v>
+        <v>-5.572402466834507</v>
       </c>
       <c r="K32" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L32" s="12" t="n">
-        <v>18.92190424183325</v>
+      <c r="L32" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M32" s="19" t="n">
-        <v>-22.79069222852237</v>
+        <v>-23.31427496150882</v>
       </c>
       <c r="N32" s="20" t="inlineStr">
         <is>
@@ -5716,28 +5712,30 @@
         </is>
       </c>
       <c r="O32" s="19" t="n">
-        <v>13.70681159853077</v>
+        <v>99.39566564852944</v>
       </c>
       <c r="P32" s="12" t="n">
-        <v>0.8541676756913837</v>
+        <v>0.2540827229386269</v>
       </c>
       <c r="Q32" s="19" t="n">
-        <v>25.49012345679012</v>
+        <v>0</v>
       </c>
       <c r="R32" s="19" t="n">
-        <v>73.97555858249444</v>
+        <v>72.87233657839809</v>
       </c>
       <c r="S32" s="21" t="n">
-        <v>0.3935340579926538</v>
+        <v>0.2767857142857142</v>
       </c>
       <c r="T32" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U32" s="21" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="V32" s="12" t="n">
-        <v>2.395606518518519</v>
+        <v>0.25</v>
+      </c>
+      <c r="V32" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -5746,26 +5744,26 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>CCDBF</t>
+          <t>CNPRF</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>CCL Industries Inc.</t>
+          <t>Condor Petroleum Inc.</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="F33" s="10" t="n">
-        <v>10936875008</v>
+        <v>194044128</v>
       </c>
       <c r="G33" s="17" t="inlineStr">
         <is>
@@ -5773,22 +5771,24 @@
         </is>
       </c>
       <c r="H33" s="18" t="n">
-        <v>0.1957910339720751</v>
+        <v>0.2117914394277349</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>0.2095771487780788</v>
+        <v>0.2925786992611523</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>7.412301545870455</v>
-      </c>
-      <c r="K33" s="12" t="n">
-        <v>19.763975</v>
+        <v>11.09411110572964</v>
+      </c>
+      <c r="K33" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L33" s="12" t="n">
-        <v>1.949045694122679</v>
+        <v>18.92190424183325</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>7.87702153832642</v>
+        <v>-22.79069222852237</v>
       </c>
       <c r="N33" s="20" t="inlineStr">
         <is>
@@ -5796,28 +5796,28 @@
         </is>
       </c>
       <c r="O33" s="19" t="n">
-        <v>16.58105227009315</v>
+        <v>13.70681159853077</v>
       </c>
       <c r="P33" s="12" t="n">
-        <v>0.7104502769082591</v>
+        <v>0.8541676756913837</v>
       </c>
       <c r="Q33" s="19" t="n">
-        <v>21.53012688414531</v>
+        <v>25.49012345679012</v>
       </c>
       <c r="R33" s="19" t="n">
-        <v>10.35260377825765</v>
+        <v>73.97555858249444</v>
       </c>
       <c r="S33" s="21" t="n">
-        <v>0.4979619216117169</v>
+        <v>0.3935340579926538</v>
       </c>
       <c r="T33" s="15" t="n">
         <v>0</v>
       </c>
       <c r="U33" s="21" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="V33" s="12" t="n">
-        <v>1.417483184675402</v>
+        <v>2.395606518518519</v>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
@@ -5826,26 +5826,26 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>NCPCF</t>
+          <t>APYRF</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Nickel Creek Platinum Corp.</t>
+          <t>Allied Properties Real Estate Investment Trust</t>
         </is>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="F34" s="10" t="n">
-        <v>10223689</v>
+        <v>1494534656</v>
       </c>
       <c r="G34" s="17" t="inlineStr">
         <is>
@@ -5853,13 +5853,13 @@
         </is>
       </c>
       <c r="H34" s="18" t="n">
-        <v>0.1835052364268266</v>
+        <v>0.2034341944125864</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>0.2177178299940457</v>
+        <v>0.206179462256708</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>-6.261270083918534</v>
+        <v>-4.531926963057693</v>
       </c>
       <c r="K34" s="20" t="inlineStr">
         <is>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="L34" s="12" t="n">
-        <v>11.65872669238568</v>
+        <v>0.3416135433543135</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>-6.6333492734374</v>
+        <v>11.27340870441481</v>
       </c>
       <c r="N34" s="20" t="inlineStr">
         <is>
@@ -5878,32 +5878,28 @@
         </is>
       </c>
       <c r="O34" s="19" t="n">
-        <v>211.768912734098</v>
-      </c>
-      <c r="P34" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.24806584122181</v>
+      </c>
+      <c r="P34" s="12" t="n">
+        <v>-2.157813933075331</v>
       </c>
       <c r="Q34" s="19" t="n">
-        <v>0</v>
+        <v>-208.1197801413377</v>
       </c>
       <c r="R34" s="19" t="n">
-        <v>34.25925833943453</v>
+        <v>-43.10345984005884</v>
       </c>
       <c r="S34" s="21" t="n">
-        <v>0.2279411764705882</v>
+        <v>0.5880755468164794</v>
       </c>
       <c r="T34" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" s="21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V34" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.429</v>
+      </c>
+      <c r="V34" s="12" t="n">
+        <v>2.540092688713718</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -5912,26 +5908,26 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>SNNGF</t>
+          <t>CCDBF</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>PPX Mining Corp.</t>
+          <t>CCL Industries Inc.</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="F35" s="10" t="n">
-        <v>113023296</v>
+        <v>10936875008</v>
       </c>
       <c r="G35" s="17" t="inlineStr">
         <is>
@@ -5939,26 +5935,22 @@
         </is>
       </c>
       <c r="H35" s="18" t="n">
-        <v>0.1808444555035764</v>
+        <v>0.1957910339720751</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>0.2602200333885721</v>
+        <v>0.2095771487780788</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>-5.572402466834507</v>
-      </c>
-      <c r="K35" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L35" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>7.412301545870455</v>
+      </c>
+      <c r="K35" s="12" t="n">
+        <v>19.763975</v>
+      </c>
+      <c r="L35" s="12" t="n">
+        <v>1.949045694122679</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>-23.31427496150882</v>
+        <v>7.87702153832642</v>
       </c>
       <c r="N35" s="20" t="inlineStr">
         <is>
@@ -5966,32 +5958,28 @@
         </is>
       </c>
       <c r="O35" s="19" t="n">
-        <v>99.39566564852944</v>
-      </c>
-      <c r="P35" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>16.58105227009315</v>
+      </c>
+      <c r="P35" s="12" t="n">
+        <v>0.7104502769082591</v>
       </c>
       <c r="Q35" s="19" t="n">
+        <v>21.53012688414531</v>
+      </c>
+      <c r="R35" s="19" t="n">
+        <v>10.35260377825765</v>
+      </c>
+      <c r="S35" s="21" t="n">
+        <v>0.4979619216117169</v>
+      </c>
+      <c r="T35" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="R35" s="19" t="n">
-        <v>72.87233657839809</v>
-      </c>
-      <c r="S35" s="21" t="n">
-        <v>0.2767857142857142</v>
-      </c>
-      <c r="T35" s="15" t="n">
-        <v>1</v>
-      </c>
       <c r="U35" s="21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V35" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.8</v>
+      </c>
+      <c r="V35" s="12" t="n">
+        <v>1.417483184675402</v>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
@@ -6000,26 +5988,26 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>SNWGF</t>
+          <t>AHOTF</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Snowline Gold Corp.</t>
+          <t>American Hotel Income Properties REIT LP</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="F36" s="10" t="n">
-        <v>1636027136</v>
+        <v>30133950</v>
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
@@ -6027,13 +6015,13 @@
         </is>
       </c>
       <c r="H36" s="18" t="n">
-        <v>0.1623333768445994</v>
+        <v>0.1924903747144942</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>0.2014306575934205</v>
+        <v>0.2034072947585613</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>-26.44863029157462</v>
+        <v>-26.62213312202853</v>
       </c>
       <c r="K36" s="20" t="inlineStr">
         <is>
@@ -6041,45 +6029,39 @@
         </is>
       </c>
       <c r="L36" s="12" t="n">
-        <v>13.90753796456867</v>
+        <v>0.6355228193015016</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>-3.80361649453716</v>
+        <v>-31.44294060353853</v>
       </c>
       <c r="N36" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O36" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P36" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="O36" s="19" t="n">
+        <v>5.05193453788667</v>
+      </c>
+      <c r="P36" s="12" t="n">
+        <v>-21.44641442155309</v>
       </c>
       <c r="Q36" s="19" t="n">
-        <v>0</v>
+        <v>-5.75162505056029</v>
       </c>
       <c r="R36" s="19" t="n">
-        <v>40.97116459405312</v>
+        <v>23.52940660859479</v>
       </c>
       <c r="S36" s="21" t="n">
-        <v>0.1078615430340557</v>
+        <v>0.2910408497258411</v>
       </c>
       <c r="T36" s="15" t="n">
         <v>0</v>
       </c>
       <c r="U36" s="21" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="V36" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.375</v>
+      </c>
+      <c r="V36" s="12" t="n">
+        <v>0.1716711387602331</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -6088,17 +6070,17 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>GARLF</t>
+          <t>NCPCF</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Netcoins Holdings Inc.</t>
+          <t>Nickel Creek Platinum Corp.</t>
         </is>
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -6107,7 +6089,7 @@
         </is>
       </c>
       <c r="F37" s="10" t="n">
-        <v>140777808</v>
+        <v>10223689</v>
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
@@ -6115,13 +6097,13 @@
         </is>
       </c>
       <c r="H37" s="18" t="n">
-        <v>0.1605134271065026</v>
+        <v>0.1835052364268266</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>0.244270405203262</v>
+        <v>0.2177178299940457</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>-8.32514019814637</v>
+        <v>-6.261270083918534</v>
       </c>
       <c r="K37" s="20" t="inlineStr">
         <is>
@@ -6129,10 +6111,10 @@
         </is>
       </c>
       <c r="L37" s="12" t="n">
-        <v>1.868286485742727</v>
+        <v>11.65872669238568</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>-11.93534850322431</v>
+        <v>-6.6333492734374</v>
       </c>
       <c r="N37" s="20" t="inlineStr">
         <is>
@@ -6140,24 +6122,22 @@
         </is>
       </c>
       <c r="O37" s="19" t="n">
-        <v>-39.59833597578566</v>
-      </c>
-      <c r="P37" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>211.768912734098</v>
+      </c>
+      <c r="P37" s="12" t="n">
+        <v>0.8035681876381392</v>
       </c>
       <c r="Q37" s="19" t="n">
         <v>0</v>
       </c>
       <c r="R37" s="19" t="n">
-        <v>114.1304340079737</v>
+        <v>34.25925833943453</v>
       </c>
       <c r="S37" s="21" t="n">
-        <v>0.2136580479151857</v>
+        <v>0.2279411764705882</v>
       </c>
       <c r="T37" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U37" s="21" t="n">
         <v>0.25</v>
@@ -6174,26 +6154,26 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>SKKY</t>
+          <t>HRUFF</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Skkynet Cloud Systems, Inc.</t>
+          <t>H&amp;R Real Estate Investment Trust</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="F38" s="10" t="n">
-        <v>18600338</v>
+        <v>2209270272</v>
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
@@ -6201,13 +6181,13 @@
         </is>
       </c>
       <c r="H38" s="18" t="n">
-        <v>0.1560071112976548</v>
+        <v>0.1663690243850831</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>0.1826392570064554</v>
+        <v>0.1811411251348143</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>-47.25445320352139</v>
+        <v>-5.708685331388856</v>
       </c>
       <c r="K38" s="20" t="inlineStr">
         <is>
@@ -6215,10 +6195,10 @@
         </is>
       </c>
       <c r="L38" s="12" t="n">
-        <v>22.22262604540024</v>
+        <v>0.5365411131101103</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>-0.48793736974027</v>
+        <v>5.96391494829293</v>
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
@@ -6226,30 +6206,28 @@
         </is>
       </c>
       <c r="O38" s="19" t="n">
-        <v>147.9515112486509</v>
-      </c>
-      <c r="P38" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>7.46965997269992</v>
+      </c>
+      <c r="P38" s="12" t="n">
+        <v>-3.010340533875332</v>
       </c>
       <c r="Q38" s="19" t="n">
-        <v>-32.93530758898922</v>
+        <v>-104.0118829544109</v>
       </c>
       <c r="R38" s="19" t="n">
-        <v>-14.99999840344702</v>
+        <v>-11.26712246858492</v>
       </c>
       <c r="S38" s="21" t="n">
-        <v>0.2874999960086175</v>
+        <v>0.4456558599949168</v>
       </c>
       <c r="T38" s="15" t="n">
         <v>0</v>
       </c>
       <c r="U38" s="21" t="n">
-        <v>0.388</v>
+        <v>0.283</v>
       </c>
       <c r="V38" s="12" t="n">
-        <v>8.113397942723941</v>
+        <v>2.78336067891078</v>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
@@ -6258,26 +6236,26 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>APYRF</t>
+          <t>SNWGF</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Allied Properties Real Estate Investment Trust</t>
+          <t>Snowline Gold Corp.</t>
         </is>
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1494534656</v>
+        <v>1636027136</v>
       </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
@@ -6285,13 +6263,13 @@
         </is>
       </c>
       <c r="H39" s="18" t="n">
-        <v>0.1438496983943622</v>
+        <v>0.1623333768445994</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>0.145790895903114</v>
+        <v>0.2014306575934205</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>-4.531926963057693</v>
+        <v>-26.44863029157462</v>
       </c>
       <c r="K39" s="20" t="inlineStr">
         <is>
@@ -6299,41 +6277,43 @@
         </is>
       </c>
       <c r="L39" s="12" t="n">
-        <v>0.3416135433543135</v>
+        <v>13.90753796456867</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>11.27340870441481</v>
+        <v>-3.80361649453716</v>
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O39" s="19" t="n">
-        <v>1.24806584122181</v>
-      </c>
-      <c r="P39" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="O39" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P39" s="12" t="n">
+        <v>1.726575398870141</v>
       </c>
       <c r="Q39" s="19" t="n">
-        <v>-208.1197801413377</v>
+        <v>0</v>
       </c>
       <c r="R39" s="19" t="n">
-        <v>-43.10345984005884</v>
+        <v>40.97116459405312</v>
       </c>
       <c r="S39" s="21" t="n">
-        <v>0.5880755468164794</v>
+        <v>0.1078615430340557</v>
       </c>
       <c r="T39" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U39" s="21" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="V39" s="12" t="n">
-        <v>2.540092688713718</v>
+        <v>0.333</v>
+      </c>
+      <c r="V39" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
@@ -6342,26 +6322,26 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>AHOTF</t>
+          <t>GARLF</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>American Hotel Income Properties REIT LP</t>
+          <t>Netcoins Holdings Inc.</t>
         </is>
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="F40" s="10" t="n">
-        <v>30133950</v>
+        <v>140777808</v>
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
@@ -6369,13 +6349,13 @@
         </is>
       </c>
       <c r="H40" s="18" t="n">
-        <v>0.1361112492737584</v>
+        <v>0.1605134271065026</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>0.1438306774665896</v>
+        <v>0.244270405203262</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>-26.62213312202853</v>
+        <v>-8.32514019814637</v>
       </c>
       <c r="K40" s="20" t="inlineStr">
         <is>
@@ -6383,10 +6363,10 @@
         </is>
       </c>
       <c r="L40" s="12" t="n">
-        <v>0.6355228193015016</v>
+        <v>1.868286485742727</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>-31.44294060353853</v>
+        <v>-11.93534850322431</v>
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
@@ -6394,30 +6374,30 @@
         </is>
       </c>
       <c r="O40" s="19" t="n">
-        <v>5.05193453788667</v>
-      </c>
-      <c r="P40" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-39.59833597578566</v>
+      </c>
+      <c r="P40" s="12" t="n">
+        <v>3.075160416636046</v>
       </c>
       <c r="Q40" s="19" t="n">
-        <v>-5.75162505056029</v>
+        <v>0</v>
       </c>
       <c r="R40" s="19" t="n">
-        <v>23.52940660859479</v>
+        <v>114.1304340079737</v>
       </c>
       <c r="S40" s="21" t="n">
-        <v>0.2910408497258411</v>
+        <v>0.2136580479151857</v>
       </c>
       <c r="T40" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U40" s="21" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="V40" s="12" t="n">
-        <v>0.1716711387602331</v>
+        <v>0.25</v>
+      </c>
+      <c r="V40" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
@@ -6426,12 +6406,12 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>HRUFF</t>
+          <t>FCAFF</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>H&amp;R Real Estate Investment Trust</t>
+          <t>Firm Capital Apartment Real Estate Investment Trus</t>
         </is>
       </c>
       <c r="D41" s="16" t="inlineStr">
@@ -6441,11 +6421,11 @@
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="F41" s="10" t="n">
-        <v>2209270272</v>
+        <v>20912032</v>
       </c>
       <c r="G41" s="17" t="inlineStr">
         <is>
@@ -6453,24 +6433,26 @@
         </is>
       </c>
       <c r="H41" s="18" t="n">
-        <v>0.1176406653220824</v>
+        <v>0.1601753636609899</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>0.1280861179345882</v>
+        <v>0.2021267760249731</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>-5.708685331388856</v>
+        <v>-8.156624246780522</v>
       </c>
       <c r="K41" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L41" s="12" t="n">
-        <v>0.5365411131101103</v>
+      <c r="L41" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M41" s="19" t="n">
-        <v>5.96391494829293</v>
+        <v>-15.18216402882321</v>
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
@@ -6478,30 +6460,28 @@
         </is>
       </c>
       <c r="O41" s="19" t="n">
-        <v>7.46965997269992</v>
-      </c>
-      <c r="P41" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.74654209786307</v>
+      </c>
+      <c r="P41" s="12" t="n">
+        <v>-4.418429563867845</v>
       </c>
       <c r="Q41" s="19" t="n">
-        <v>-104.0118829544109</v>
+        <v>-92.02871204125088</v>
       </c>
       <c r="R41" s="19" t="n">
-        <v>-11.26712246858492</v>
+        <v>-14.06250128056852</v>
       </c>
       <c r="S41" s="21" t="n">
-        <v>0.4456558599949168</v>
+        <v>0.2633987808126313</v>
       </c>
       <c r="T41" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U41" s="21" t="n">
         <v>0.283</v>
       </c>
       <c r="V41" s="12" t="n">
-        <v>2.78336067891078</v>
+        <v>3.440212255770309</v>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
@@ -6510,17 +6490,17 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>FCAFF</t>
+          <t>SKKY</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Firm Capital Apartment Real Estate Investment Trus</t>
+          <t>Skkynet Cloud Systems, Inc.</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -6529,7 +6509,7 @@
         </is>
       </c>
       <c r="F42" s="10" t="n">
-        <v>20912032</v>
+        <v>18600338</v>
       </c>
       <c r="G42" s="17" t="inlineStr">
         <is>
@@ -6537,26 +6517,24 @@
         </is>
       </c>
       <c r="H42" s="18" t="n">
-        <v>0.1132610858237073</v>
+        <v>0.1560071112976548</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>0.142925213986633</v>
+        <v>0.1826392570064554</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>-8.156624246780522</v>
+        <v>-47.25445320352139</v>
       </c>
       <c r="K42" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L42" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L42" s="12" t="n">
+        <v>22.22262604540024</v>
       </c>
       <c r="M42" s="19" t="n">
-        <v>-15.18216402882321</v>
+        <v>-0.48793736974027</v>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
@@ -6564,30 +6542,28 @@
         </is>
       </c>
       <c r="O42" s="19" t="n">
-        <v>2.74654209786307</v>
-      </c>
-      <c r="P42" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>147.9515112486509</v>
+      </c>
+      <c r="P42" s="12" t="n">
+        <v>2.366198035867815</v>
       </c>
       <c r="Q42" s="19" t="n">
-        <v>-92.02871204125088</v>
+        <v>-32.93530758898922</v>
       </c>
       <c r="R42" s="19" t="n">
-        <v>-14.06250128056852</v>
+        <v>-14.99999840344702</v>
       </c>
       <c r="S42" s="21" t="n">
-        <v>0.2633987808126313</v>
+        <v>0.2874999960086175</v>
       </c>
       <c r="T42" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U42" s="21" t="n">
-        <v>0.283</v>
+        <v>0.388</v>
       </c>
       <c r="V42" s="12" t="n">
-        <v>3.440212255770309</v>
+        <v>8.113397942723941</v>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
@@ -6623,10 +6599,10 @@
         </is>
       </c>
       <c r="H43" s="18" t="n">
-        <v>0</v>
+        <v>0.1132084554361558</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>0</v>
+        <v>0.1694198935577238</v>
       </c>
       <c r="J43" s="12" t="n">
         <v>-5.238956088010704</v>
@@ -6652,10 +6628,8 @@
       <c r="O43" s="19" t="n">
         <v>137.85267741085</v>
       </c>
-      <c r="P43" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P43" s="12" t="n">
+        <v>-0.0821140455937148</v>
       </c>
       <c r="Q43" s="19" t="n">
         <v>-5008.380577770196</v>
@@ -7519,10 +7493,10 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="13" t="n">
-        <v>0.2572605657494061</v>
+        <v>0.2656021618524736</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.2275516379918406</v>
+        <v>0.2348501175022194</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>0.3792757336698102</v>
@@ -7946,10 +7920,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P20" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P20" s="12" t="n">
+        <v>0.409080825260667</v>
       </c>
       <c r="Q20" s="19" t="n">
         <v>-1000.962250185048</v>
@@ -8058,26 +8030,26 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>BLLYF</t>
+          <t>NXPGF</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Bluejay Mining plc</t>
+          <t>National Express Group PLC</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="F22" s="10" t="n">
-        <v>56116708</v>
+        <v>195309904</v>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
@@ -8085,24 +8057,26 @@
         </is>
       </c>
       <c r="H22" s="18" t="n">
-        <v>0.1719246843458254</v>
+        <v>0.1993485418323014</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>0.3187878727169653</v>
+        <v>0.2278399243754516</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>-1.488918466038723</v>
+        <v>-5.330104315915436</v>
       </c>
       <c r="K22" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L22" s="12" t="n">
-        <v>5.825091069098747</v>
+      <c r="L22" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M22" s="19" t="n">
-        <v>-2.04314016424484</v>
+        <v>29.18438790487552</v>
       </c>
       <c r="N22" s="20" t="inlineStr">
         <is>
@@ -8110,32 +8084,28 @@
         </is>
       </c>
       <c r="O22" s="19" t="n">
-        <v>-37.54143816697607</v>
-      </c>
-      <c r="P22" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>12.63427109974424</v>
+      </c>
+      <c r="P22" s="12" t="n">
+        <v>-5.119664938173115</v>
       </c>
       <c r="Q22" s="19" t="n">
+        <v>-7.346735435470631</v>
+      </c>
+      <c r="R22" s="19" t="n">
+        <v>-20.51281698591832</v>
+      </c>
+      <c r="S22" s="21" t="n">
+        <v>0.6665703839323111</v>
+      </c>
+      <c r="T22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="R22" s="19" t="n">
-        <v>160.0472750778964</v>
-      </c>
-      <c r="S22" s="21" t="n">
-        <v>0.1397058823529411</v>
-      </c>
-      <c r="T22" s="15" t="n">
-        <v>2</v>
-      </c>
       <c r="U22" s="21" t="n">
-        <v>0.277</v>
-      </c>
-      <c r="V22" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.833</v>
+      </c>
+      <c r="V22" s="12" t="n">
+        <v>0.0572353487281678</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -8144,26 +8114,26 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>PNXGF</t>
+          <t>BLLYF</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Phoenix Group Holdings plc</t>
+          <t>Bluejay Mining plc</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="F23" s="10" t="n">
-        <v>11623778304</v>
+        <v>56116708</v>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
@@ -8171,15 +8141,13 @@
         </is>
       </c>
       <c r="H23" s="18" t="n">
-        <v>0.1710277245953169</v>
+        <v>0.1719246843458254</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>0.1789352056688084</v>
-      </c>
-      <c r="J23" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.3187878727169653</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>-1.488918466038723</v>
       </c>
       <c r="K23" s="20" t="inlineStr">
         <is>
@@ -8187,43 +8155,41 @@
         </is>
       </c>
       <c r="L23" s="12" t="n">
-        <v>15.75037710569106</v>
+        <v>5.825091069098747</v>
       </c>
       <c r="M23" s="19" t="n">
-        <v>-8.62886381491675</v>
+        <v>-2.04314016424484</v>
       </c>
       <c r="N23" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O23" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P23" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="O23" s="19" t="n">
+        <v>-37.54143816697607</v>
+      </c>
+      <c r="P23" s="12" t="n">
+        <v>0.0364314936623846</v>
       </c>
       <c r="Q23" s="19" t="n">
-        <v>-1.53</v>
+        <v>0</v>
       </c>
       <c r="R23" s="19" t="n">
-        <v>41.98742533640278</v>
+        <v>160.0472750778964</v>
       </c>
       <c r="S23" s="21" t="n">
-        <v>0.0306176470588235</v>
+        <v>0.1397058823529411</v>
       </c>
       <c r="T23" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" s="21" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="V23" s="12" t="n">
-        <v>0.3650454840776333</v>
+        <v>0.277</v>
+      </c>
+      <c r="V23" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -8232,26 +8198,26 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>CINGF</t>
+          <t>PNXGF</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Coinsilium Group Ltd.</t>
+          <t>Phoenix Group Holdings plc</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="F24" s="10" t="n">
-        <v>14129800</v>
+        <v>11623778304</v>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
@@ -8259,13 +8225,15 @@
         </is>
       </c>
       <c r="H24" s="18" t="n">
-        <v>0.1651179909911492</v>
+        <v>0.1710277245953169</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>0.1800282359981142</v>
-      </c>
-      <c r="J24" s="12" t="n">
-        <v>-9.737297056110911</v>
+        <v>0.1789352056688084</v>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
         <is>
@@ -8273,10 +8241,10 @@
         </is>
       </c>
       <c r="L24" s="12" t="n">
-        <v>0.967774369629564</v>
+        <v>15.75037710569106</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>-8.610872057637051</v>
+        <v>-8.62886381491675</v>
       </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
@@ -8294,24 +8262,22 @@
         </is>
       </c>
       <c r="Q24" s="19" t="n">
-        <v>-21739.38333333334</v>
+        <v>-1.53</v>
       </c>
       <c r="R24" s="19" t="n">
-        <v>-91.58566686857708</v>
+        <v>41.98742533640278</v>
       </c>
       <c r="S24" s="21" t="n">
-        <v>0.4</v>
+        <v>0.0306176470588235</v>
       </c>
       <c r="T24" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" s="21" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="V24" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.35</v>
+      </c>
+      <c r="V24" s="12" t="n">
+        <v>0.3650454840776333</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -8320,26 +8286,26 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>NXPGF</t>
+          <t>CINGF</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>National Express Group PLC</t>
+          <t>Coinsilium Group Ltd.</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="F25" s="10" t="n">
-        <v>195309904</v>
+        <v>14129800</v>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
@@ -8347,34 +8313,34 @@
         </is>
       </c>
       <c r="H25" s="18" t="n">
-        <v>0.1409607057492705</v>
+        <v>0.1651179909911492</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>0.161107155550912</v>
+        <v>0.1800282359981142</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>-5.330104315915436</v>
+        <v>-9.737297056110911</v>
       </c>
       <c r="K25" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L25" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L25" s="12" t="n">
+        <v>0.967774369629564</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>29.18438790487552</v>
+        <v>-8.610872057637051</v>
       </c>
       <c r="N25" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O25" s="19" t="n">
-        <v>12.63427109974424</v>
+      <c r="O25" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="P25" s="20" t="inlineStr">
         <is>
@@ -8382,22 +8348,24 @@
         </is>
       </c>
       <c r="Q25" s="19" t="n">
-        <v>-7.346735435470631</v>
+        <v>-21739.38333333334</v>
       </c>
       <c r="R25" s="19" t="n">
-        <v>-20.51281698591832</v>
+        <v>-91.58566686857708</v>
       </c>
       <c r="S25" s="21" t="n">
-        <v>0.6665703839323111</v>
+        <v>0.4</v>
       </c>
       <c r="T25" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" s="21" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="V25" s="12" t="n">
-        <v>0.0572353487281678</v>
+        <v>0.333</v>
+      </c>
+      <c r="V25" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -9092,7 +9060,7 @@
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>BTRYF</t>
+          <t>CKDXF</t>
         </is>
       </c>
     </row>
@@ -9147,13 +9115,13 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="13" t="n">
-        <v>0.1895813301491432</v>
+        <v>0.2268826773011354</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.1434398636879123</v>
+        <v>0.169750661705388</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>0.2584026939874546</v>
+        <v>0.2826354242812499</v>
       </c>
     </row>
     <row r="12">
@@ -9169,7 +9137,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>(BTRYF)</t>
+          <t>(CKDXF)</t>
         </is>
       </c>
     </row>
@@ -9346,26 +9314,26 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>BTRYF</t>
+          <t>CKDXF</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Battery Minerals Limited</t>
+          <t>Opthea Limited</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="F18" s="10" t="n">
-        <v>124266856</v>
+        <v>13679781</v>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
@@ -9373,59 +9341,57 @@
         </is>
       </c>
       <c r="H18" s="18" t="n">
-        <v>0.2584026939874546</v>
+        <v>0.2826354242812499</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>0.3316854178740534</v>
+        <v>0.2247827529265079</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>-4.062434655221231</v>
+        <v>-0.3163631869469924</v>
       </c>
       <c r="K18" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L18" s="12" t="n">
-        <v>3.647145331456622</v>
-      </c>
-      <c r="M18" s="19" t="n">
-        <v>-10.12619487210652</v>
+      <c r="L18" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M18" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O18" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P18" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="O18" s="19" t="n">
+        <v>106.2340452243782</v>
+      </c>
+      <c r="P18" s="12" t="n">
+        <v>-0.2053169900154233</v>
       </c>
       <c r="Q18" s="19" t="n">
-        <v>0</v>
+        <v>-492760.0000000001</v>
       </c>
       <c r="R18" s="19" t="n">
-        <v>51.16980794160207</v>
+        <v>-97.72727276575712</v>
       </c>
       <c r="S18" s="21" t="n">
-        <v>0.1560706716235791</v>
+        <v>0.5588235294117646</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>2</v>
       </c>
       <c r="U18" s="21" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V18" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="V18" s="12" t="n">
+        <v>547.19124</v>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
@@ -9434,17 +9400,17 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>JAXAF</t>
+          <t>BTRYF</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Jaxsta Limited</t>
+          <t>Battery Minerals Limited</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -9453,7 +9419,7 @@
         </is>
       </c>
       <c r="F19" s="10" t="n">
-        <v>74158808</v>
+        <v>124266856</v>
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
@@ -9461,13 +9427,13 @@
         </is>
       </c>
       <c r="H19" s="18" t="n">
-        <v>0.2575164595422941</v>
+        <v>0.2584026939874546</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>0.2890565646660943</v>
+        <v>0.3316854178740534</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>-4.937442391604431</v>
+        <v>-4.062434655221231</v>
       </c>
       <c r="K19" s="20" t="inlineStr">
         <is>
@@ -9475,41 +9441,43 @@
         </is>
       </c>
       <c r="L19" s="12" t="n">
-        <v>4.103707490377078</v>
+        <v>3.647145331456622</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>-12.09961600245786</v>
+        <v>-10.12619487210652</v>
       </c>
       <c r="N19" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O19" s="19" t="n">
-        <v>-73.77108387646696</v>
-      </c>
-      <c r="P19" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="O19" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P19" s="12" t="n">
+        <v>1.64714997535844</v>
       </c>
       <c r="Q19" s="19" t="n">
-        <v>-96.82175235815323</v>
+        <v>0</v>
       </c>
       <c r="R19" s="19" t="n">
-        <v>25.00000465661298</v>
+        <v>51.16980794160207</v>
       </c>
       <c r="S19" s="21" t="n">
-        <v>0.1206903794108695</v>
+        <v>0.1560706716235791</v>
       </c>
       <c r="T19" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U19" s="21" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="V19" s="12" t="n">
-        <v>5.148765900958258</v>
+        <v>0.02</v>
+      </c>
+      <c r="V19" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
@@ -9518,26 +9486,26 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>RDBBF</t>
+          <t>JAXAF</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Redbubble Limited</t>
+          <t>Jaxsta Limited</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="F20" s="10" t="n">
-        <v>57850032</v>
+        <v>74158808</v>
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
@@ -9545,22 +9513,24 @@
         </is>
       </c>
       <c r="H20" s="18" t="n">
-        <v>0.2547111829661684</v>
+        <v>0.2575164595422941</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>0.2759280939642938</v>
+        <v>0.2890565646660943</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>13.48147959565706</v>
-      </c>
-      <c r="K20" s="12" t="n">
-        <v>19</v>
+        <v>-4.937442391604431</v>
+      </c>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L20" s="12" t="n">
-        <v>1.261668673122219</v>
+        <v>4.103707490377078</v>
       </c>
       <c r="M20" s="19" t="n">
-        <v>-7.95159456437292</v>
+        <v>-12.09961600245786</v>
       </c>
       <c r="N20" s="20" t="inlineStr">
         <is>
@@ -9568,28 +9538,28 @@
         </is>
       </c>
       <c r="O20" s="19" t="n">
-        <v>-28.19124567906376</v>
+        <v>-73.77108387646696</v>
       </c>
       <c r="P20" s="12" t="n">
-        <v>-8.177087233245976</v>
+        <v>0.1279967301162745</v>
       </c>
       <c r="Q20" s="19" t="n">
-        <v>0.60892204156445</v>
+        <v>-96.82175235815323</v>
       </c>
       <c r="R20" s="19" t="n">
-        <v>35.71428343349574</v>
+        <v>25.00000465661298</v>
       </c>
       <c r="S20" s="21" t="n">
-        <v>0.2321461671527257</v>
+        <v>0.1206903794108695</v>
       </c>
       <c r="T20" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U20" s="21" t="n">
-        <v>0.333</v>
+        <v>0.525</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>0.1318837873081587</v>
+        <v>5.148765900958258</v>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
@@ -9598,26 +9568,26 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>FARYF</t>
+          <t>RDBBF</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>FAR Limited</t>
+          <t>Redbubble Limited</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="F21" s="10" t="n">
-        <v>18075328</v>
+        <v>57850032</v>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
@@ -9625,59 +9595,51 @@
         </is>
       </c>
       <c r="H21" s="18" t="n">
-        <v>0.2478784350483716</v>
+        <v>0.2547111829661684</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>0.2404886194213583</v>
+        <v>0.2759280939642938</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>-24.0152955650002</v>
-      </c>
-      <c r="K21" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>13.48147959565706</v>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>19</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>0.4401419298647353</v>
+        <v>1.261668673122219</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>-3.0780962868281</v>
+        <v>-7.95159456437292</v>
       </c>
       <c r="N21" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O21" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P21" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="O21" s="19" t="n">
+        <v>-28.19124567906376</v>
+      </c>
+      <c r="P21" s="12" t="n">
+        <v>-8.177087233245976</v>
       </c>
       <c r="Q21" s="19" t="n">
+        <v>0.60892204156445</v>
+      </c>
+      <c r="R21" s="19" t="n">
+        <v>35.71428343349574</v>
+      </c>
+      <c r="S21" s="21" t="n">
+        <v>0.2321461671527257</v>
+      </c>
+      <c r="T21" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="R21" s="19" t="n">
-        <v>-14.0597501227087</v>
-      </c>
-      <c r="S21" s="21" t="n">
-        <v>0.467822794478555</v>
-      </c>
-      <c r="T21" s="15" t="n">
-        <v>1</v>
-      </c>
       <c r="U21" s="21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V21" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.333</v>
+      </c>
+      <c r="V21" s="12" t="n">
+        <v>0.1318837873081587</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -9686,26 +9648,26 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>AUSDF</t>
+          <t>FARYF</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Perenti Global Limited</t>
+          <t>FAR Limited</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1607856640</v>
+        <v>18075328</v>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
@@ -9713,51 +9675,59 @@
         </is>
       </c>
       <c r="H22" s="18" t="n">
-        <v>0.2395583464751971</v>
+        <v>0.2478784350483716</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>0.3413071535187108</v>
+        <v>0.2404886194213583</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>3.191019080882573</v>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>19.11111</v>
+        <v>-24.0152955650002</v>
+      </c>
+      <c r="K22" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L22" s="12" t="n">
-        <v>0.8792732443044482</v>
+        <v>0.4401419298647353</v>
       </c>
       <c r="M22" s="19" t="n">
-        <v>12.4168408447161</v>
+        <v>-3.0780962868281</v>
       </c>
       <c r="N22" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O22" s="19" t="n">
-        <v>10.63711303672828</v>
-      </c>
-      <c r="P22" s="12" t="n">
-        <v>0.3960870711294564</v>
+      <c r="O22" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P22" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q22" s="19" t="n">
-        <v>19.13383574826066</v>
+        <v>0</v>
       </c>
       <c r="R22" s="19" t="n">
-        <v>98.93898725463231</v>
+        <v>-14.0597501227087</v>
       </c>
       <c r="S22" s="21" t="n">
-        <v>0.7312901747077343</v>
+        <v>0.467822794478555</v>
       </c>
       <c r="T22" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22" s="21" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="V22" s="12" t="n">
-        <v>0.4607638472168012</v>
+        <v>0.25</v>
+      </c>
+      <c r="V22" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -9766,17 +9736,17 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>CKDXF</t>
+          <t>AUSDF</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Opthea Limited</t>
+          <t>Perenti Global Limited</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -9785,7 +9755,7 @@
         </is>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13679781</v>
+        <v>1607856640</v>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
@@ -9793,28 +9763,22 @@
         </is>
       </c>
       <c r="H23" s="18" t="n">
-        <v>0.1998534251128088</v>
+        <v>0.2395583464751971</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>0.158945408888114</v>
+        <v>0.3413071535187108</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>-0.3163631869469924</v>
-      </c>
-      <c r="K23" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L23" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M23" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>3.191019080882573</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>19.11111</v>
+      </c>
+      <c r="L23" s="12" t="n">
+        <v>0.8792732443044482</v>
+      </c>
+      <c r="M23" s="19" t="n">
+        <v>12.4168408447161</v>
       </c>
       <c r="N23" s="20" t="inlineStr">
         <is>
@@ -9822,30 +9786,28 @@
         </is>
       </c>
       <c r="O23" s="19" t="n">
-        <v>106.2340452243782</v>
-      </c>
-      <c r="P23" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>10.63711303672828</v>
+      </c>
+      <c r="P23" s="12" t="n">
+        <v>0.3960870711294564</v>
       </c>
       <c r="Q23" s="19" t="n">
-        <v>-492760.0000000001</v>
+        <v>19.13383574826066</v>
       </c>
       <c r="R23" s="19" t="n">
-        <v>-97.72727276575712</v>
+        <v>98.93898725463231</v>
       </c>
       <c r="S23" s="21" t="n">
-        <v>0.5588235294117646</v>
+        <v>0.7312901747077343</v>
       </c>
       <c r="T23" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U23" s="21" t="n">
-        <v>1</v>
+        <v>0.889</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>547.19124</v>
+        <v>0.4607638472168012</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -9908,10 +9870,8 @@
       <c r="O24" s="19" t="n">
         <v>-9.077445689902531</v>
       </c>
-      <c r="P24" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P24" s="12" t="n">
+        <v>13.04583746283449</v>
       </c>
       <c r="Q24" s="19" t="n">
         <v>0</v>
@@ -9940,26 +9900,26 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>EEENF</t>
+          <t>MIGI</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>88 Energy Ltd.</t>
+          <t>Mawson Infrastructure Group Inc.</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="F25" s="10" t="n">
-        <v>25421200</v>
+        <v>25842498</v>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
@@ -9967,13 +9927,13 @@
         </is>
       </c>
       <c r="H25" s="18" t="n">
-        <v>0.1758821597004321</v>
+        <v>0.1893896651249714</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>0.1776708183840661</v>
+        <v>0.2104329612499682</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>-0.2888686710788206</v>
+        <v>-3.175526258048871</v>
       </c>
       <c r="K25" s="20" t="inlineStr">
         <is>
@@ -9981,45 +9941,39 @@
         </is>
       </c>
       <c r="L25" s="12" t="n">
-        <v>0.2901354682643588</v>
+        <v>5.949095946833483</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>-35.48332100766289</v>
+        <v>-91.73126761971696</v>
       </c>
       <c r="N25" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O25" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P25" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="O25" s="19" t="n">
+        <v>-78.58316854829572</v>
+      </c>
+      <c r="P25" s="12" t="n">
+        <v>-1.914749630151232</v>
       </c>
       <c r="Q25" s="19" t="n">
+        <v>-40.84936564562794</v>
+      </c>
+      <c r="R25" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="R25" s="19" t="n">
-        <v>31.72413633637985</v>
-      </c>
       <c r="S25" s="21" t="n">
-        <v>0.338235294117647</v>
+        <v>0.325</v>
       </c>
       <c r="T25" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="U25" s="21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V25" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="V25" s="12" t="n">
+        <v>0.8401328152798365</v>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
@@ -10028,26 +9982,26 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>MIGI</t>
+          <t>EEENF</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Mawson Infrastructure Group Inc.</t>
+          <t>88 Energy Ltd.</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="F26" s="10" t="n">
-        <v>25842498</v>
+        <v>25421200</v>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
@@ -10055,13 +10009,13 @@
         </is>
       </c>
       <c r="H26" s="18" t="n">
-        <v>0.1339187164965166</v>
+        <v>0.1758821597004321</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>0.1487985738850185</v>
+        <v>0.1776708183840661</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>-3.175526258048871</v>
+        <v>-0.2888686710788206</v>
       </c>
       <c r="K26" s="20" t="inlineStr">
         <is>
@@ -10069,18 +10023,20 @@
         </is>
       </c>
       <c r="L26" s="12" t="n">
-        <v>5.949095946833483</v>
+        <v>0.2901354682643588</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>-91.73126761971696</v>
+        <v>-35.48332100766289</v>
       </c>
       <c r="N26" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O26" s="19" t="n">
-        <v>-78.58316854829572</v>
+      <c r="O26" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="P26" s="20" t="inlineStr">
         <is>
@@ -10088,22 +10044,24 @@
         </is>
       </c>
       <c r="Q26" s="19" t="n">
-        <v>-40.84936564562794</v>
+        <v>0</v>
       </c>
       <c r="R26" s="19" t="n">
-        <v>0</v>
+        <v>31.72413633637985</v>
       </c>
       <c r="S26" s="21" t="n">
-        <v>0.325</v>
+        <v>0.338235294117647</v>
       </c>
       <c r="T26" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U26" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="12" t="n">
-        <v>0.8401328152798365</v>
+        <v>0.25</v>
+      </c>
+      <c r="V26" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -10112,26 +10070,26 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>HEGLF</t>
+          <t>ADPXY</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Peak Minerals Limited</t>
+          <t>Audio Pixels Holdings Limited</t>
         </is>
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="F27" s="10" t="n">
-        <v>75513328</v>
+        <v>87630304</v>
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
@@ -10139,24 +10097,26 @@
         </is>
       </c>
       <c r="H27" s="18" t="n">
-        <v>0.09328822535247329</v>
+        <v>0.14415029548894</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>0.1213505370438677</v>
+        <v>0.1813211264011823</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>-9.75445937129772</v>
+        <v>-19.46309139327582</v>
       </c>
       <c r="K27" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L27" s="12" t="n">
-        <v>96.96225046257597</v>
+      <c r="L27" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M27" s="19" t="n">
-        <v>-3.58360050029843</v>
+        <v>-7.116439993178609</v>
       </c>
       <c r="N27" s="20" t="inlineStr">
         <is>
@@ -10168,25 +10128,23 @@
           <t>–</t>
         </is>
       </c>
-      <c r="P27" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P27" s="12" t="n">
+        <v>-2.097316671176232</v>
       </c>
       <c r="Q27" s="19" t="n">
         <v>0</v>
       </c>
       <c r="R27" s="19" t="n">
-        <v>-31.30000154599551</v>
+        <v>24.79201103390056</v>
       </c>
       <c r="S27" s="21" t="n">
-        <v>0.338235294117647</v>
+        <v>0.2953856748789265</v>
       </c>
       <c r="T27" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27" s="21" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="V27" s="20" t="inlineStr">
         <is>
@@ -10200,17 +10158,17 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>STRXF</t>
+          <t>HEGLF</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Pure Hydrogen Corporation Limited</t>
+          <t>Peak Minerals Limited</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -10219,7 +10177,7 @@
         </is>
       </c>
       <c r="F28" s="10" t="n">
-        <v>16870864</v>
+        <v>75513328</v>
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
@@ -10227,13 +10185,13 @@
         </is>
       </c>
       <c r="H28" s="18" t="n">
-        <v>0.08543869995860529</v>
+        <v>0.09328822535247329</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>0.2637305854559421</v>
+        <v>0.1213505370438677</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>-15.75633187116933</v>
+        <v>-9.75445937129772</v>
       </c>
       <c r="K28" s="20" t="inlineStr">
         <is>
@@ -10241,18 +10199,20 @@
         </is>
       </c>
       <c r="L28" s="12" t="n">
-        <v>4.063533353951036</v>
+        <v>96.96225046257597</v>
       </c>
       <c r="M28" s="19" t="n">
-        <v>-1.11633286831071</v>
+        <v>-3.58360050029843</v>
       </c>
       <c r="N28" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O28" s="19" t="n">
-        <v>-29.80534549181498</v>
+      <c r="O28" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="P28" s="20" t="inlineStr">
         <is>
@@ -10263,16 +10223,16 @@
         <v>0</v>
       </c>
       <c r="R28" s="19" t="n">
-        <v>413.9470995202627</v>
+        <v>-31.30000154599551</v>
       </c>
       <c r="S28" s="21" t="n">
-        <v>0.1498730697177446</v>
+        <v>0.338235294117647</v>
       </c>
       <c r="T28" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U28" s="21" t="n">
-        <v>0.263</v>
+        <v>0</v>
       </c>
       <c r="V28" s="20" t="inlineStr">
         <is>
@@ -10286,26 +10246,26 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>FDMDF</t>
+          <t>STRXF</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>4DMedical Limited</t>
+          <t>Pure Hydrogen Corporation Limited</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1673452544</v>
+        <v>16870864</v>
       </c>
       <c r="G29" s="17" t="inlineStr">
         <is>
@@ -10313,13 +10273,13 @@
         </is>
       </c>
       <c r="H29" s="18" t="n">
-        <v>0.07878218273982707</v>
+        <v>0.08543869995860529</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>0.2339925213767321</v>
+        <v>0.2637305854559421</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>-58.38105803114753</v>
+        <v>-15.75633187116933</v>
       </c>
       <c r="K29" s="20" t="inlineStr">
         <is>
@@ -10327,10 +10287,10 @@
         </is>
       </c>
       <c r="L29" s="12" t="n">
-        <v>26.05196926013967</v>
+        <v>4.063533353951036</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>-2.07706493528148</v>
+        <v>-1.11633286831071</v>
       </c>
       <c r="N29" s="20" t="inlineStr">
         <is>
@@ -10338,30 +10298,30 @@
         </is>
       </c>
       <c r="O29" s="19" t="n">
-        <v>-77.15078590392838</v>
-      </c>
-      <c r="P29" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-29.80534549181498</v>
+      </c>
+      <c r="P29" s="12" t="n">
+        <v>0.0835461482994832</v>
       </c>
       <c r="Q29" s="19" t="n">
-        <v>-429.5696335370287</v>
+        <v>0</v>
       </c>
       <c r="R29" s="19" t="n">
-        <v>1128.609026612206</v>
+        <v>413.9470995202627</v>
       </c>
       <c r="S29" s="21" t="n">
-        <v>0.0747547459368421</v>
+        <v>0.1498730697177446</v>
       </c>
       <c r="T29" s="15" t="n">
         <v>2</v>
       </c>
       <c r="U29" s="21" t="n">
-        <v>0.483</v>
-      </c>
-      <c r="V29" s="12" t="n">
-        <v>289.6047788999068</v>
+        <v>0.263</v>
+      </c>
+      <c r="V29" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -10370,26 +10330,26 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>ALTAF</t>
+          <t>FDMDF</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Altura Mining Limited</t>
+          <t>4DMedical Limited</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="F30" s="10" t="n">
-        <v>21450490</v>
+        <v>1673452544</v>
       </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
@@ -10397,13 +10357,13 @@
         </is>
       </c>
       <c r="H30" s="18" t="n">
-        <v>0.07057962933553408</v>
+        <v>0.07878218273982707</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0.2181615644644352</v>
+        <v>0.2339925213767321</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>-8.706980478059428</v>
+        <v>-58.38105803114753</v>
       </c>
       <c r="K30" s="20" t="inlineStr">
         <is>
@@ -10411,10 +10371,10 @@
         </is>
       </c>
       <c r="L30" s="12" t="n">
-        <v>2.746349614994906</v>
+        <v>26.05196926013967</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>-40.27040407934737</v>
+        <v>-2.07706493528148</v>
       </c>
       <c r="N30" s="20" t="inlineStr">
         <is>
@@ -10422,30 +10382,28 @@
         </is>
       </c>
       <c r="O30" s="19" t="n">
-        <v>-26.19278722449802</v>
-      </c>
-      <c r="P30" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-77.15078590392838</v>
+      </c>
+      <c r="P30" s="12" t="n">
+        <v>0.1035640757230124</v>
       </c>
       <c r="Q30" s="19" t="n">
-        <v>-499.0243253515773</v>
+        <v>-429.5696335370287</v>
       </c>
       <c r="R30" s="19" t="n">
-        <v>662.3188501648407</v>
+        <v>1128.609026612206</v>
       </c>
       <c r="S30" s="21" t="n">
-        <v>0.1307724438928901</v>
+        <v>0.0747547459368421</v>
       </c>
       <c r="T30" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U30" s="21" t="n">
-        <v>0.392</v>
+        <v>0.483</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>40.76489927784112</v>
+        <v>289.6047788999068</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -10481,10 +10439,10 @@
         </is>
       </c>
       <c r="H31" s="18" t="n">
-        <v>0</v>
+        <v>0.0751997088764472</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>0</v>
+        <v>0.1002662785019296</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>-127.3747340832894</v>
@@ -10508,10 +10466,8 @@
       <c r="O31" s="19" t="n">
         <v>-30.40726347524528</v>
       </c>
-      <c r="P31" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P31" s="12" t="n">
+        <v>-4.017307986861587</v>
       </c>
       <c r="Q31" s="19" t="n">
         <v>-93.31565239486724</v>
@@ -10538,12 +10494,12 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>SRMMF</t>
+          <t>ALTAF</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Sarama Resources Ltd</t>
+          <t>Altura Mining Limited</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
@@ -10553,11 +10509,11 @@
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="F32" s="10" t="n">
-        <v>20212274</v>
+        <v>21450490</v>
       </c>
       <c r="G32" s="17" t="inlineStr">
         <is>
@@ -10565,26 +10521,24 @@
         </is>
       </c>
       <c r="H32" s="18" t="n">
-        <v>0</v>
+        <v>0.07057962933553408</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>0</v>
+        <v>0.2181615644644352</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>-6.887776568791873</v>
+        <v>-8.706980478059428</v>
       </c>
       <c r="K32" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L32" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L32" s="12" t="n">
+        <v>2.746349614994906</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>-9.258245757008829</v>
+        <v>-40.27040407934737</v>
       </c>
       <c r="N32" s="20" t="inlineStr">
         <is>
@@ -10592,32 +10546,28 @@
         </is>
       </c>
       <c r="O32" s="19" t="n">
-        <v>185.3552086215862</v>
-      </c>
-      <c r="P32" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-26.19278722449802</v>
+      </c>
+      <c r="P32" s="12" t="n">
+        <v>-1.180259769538887</v>
       </c>
       <c r="Q32" s="19" t="n">
-        <v>0</v>
+        <v>-499.0243253515773</v>
       </c>
       <c r="R32" s="19" t="n">
-        <v>2274.999983629095</v>
+        <v>662.3188501648407</v>
       </c>
       <c r="S32" s="21" t="n">
-        <v>0.2767857142857142</v>
+        <v>0.1307724438928901</v>
       </c>
       <c r="T32" s="15" t="n">
         <v>1</v>
       </c>
       <c r="U32" s="21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V32" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.392</v>
+      </c>
+      <c r="V32" s="12" t="n">
+        <v>40.76489927784112</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -10626,26 +10576,26 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>ADPXY</t>
+          <t>SRMMF</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Audio Pixels Holdings Limited</t>
+          <t>Sarama Resources Ltd</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="F33" s="10" t="n">
-        <v>87630304</v>
+        <v>20212274</v>
       </c>
       <c r="G33" s="17" t="inlineStr">
         <is>
@@ -10653,13 +10603,13 @@
         </is>
       </c>
       <c r="H33" s="18" t="n">
-        <v>0</v>
+        <v>0.06336981611732885</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>0</v>
+        <v>0.1877624181254188</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>-19.46309139327582</v>
+        <v>-6.887776568791873</v>
       </c>
       <c r="K33" s="20" t="inlineStr">
         <is>
@@ -10672,37 +10622,33 @@
         </is>
       </c>
       <c r="M33" s="19" t="n">
-        <v>-7.116439993178609</v>
+        <v>-9.258245757008829</v>
       </c>
       <c r="N33" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O33" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P33" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="O33" s="19" t="n">
+        <v>185.3552086215862</v>
+      </c>
+      <c r="P33" s="12" t="n">
+        <v>-0.0402464951569368</v>
       </c>
       <c r="Q33" s="19" t="n">
         <v>0</v>
       </c>
       <c r="R33" s="19" t="n">
-        <v>24.79201103390056</v>
+        <v>2274.999983629095</v>
       </c>
       <c r="S33" s="21" t="n">
-        <v>0.2953856748789265</v>
+        <v>0.2767857142857142</v>
       </c>
       <c r="T33" s="15" t="n">
         <v>1</v>
       </c>
       <c r="U33" s="21" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="V33" s="20" t="inlineStr">
         <is>
@@ -10907,10 +10853,10 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="13" t="n">
-        <v>0.2796916077448598</v>
+        <v>0.2866767447142748</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.288971026221657</v>
+        <v>0.2945080204183401</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>1.163700926871588</v>
@@ -11240,10 +11186,8 @@
       <c r="O19" s="19" t="n">
         <v>7.663891169227161</v>
       </c>
-      <c r="P19" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P19" s="12" t="n">
+        <v>3.420340681362725</v>
       </c>
       <c r="Q19" s="19" t="n">
         <v>-8.12521625857401</v>
@@ -12076,26 +12020,26 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>NXCLF</t>
+          <t>GLPGF</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>LIFULL Co., Ltd.</t>
+          <t>Lakefront Biotherapeutics</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="F30" s="10" t="n">
-        <v>202778128</v>
+        <v>3189103616</v>
       </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
@@ -12103,24 +12047,22 @@
         </is>
       </c>
       <c r="H30" s="18" t="n">
-        <v>0.8938697664316019</v>
+        <v>0.881989217820347</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0.5358060628784111</v>
+        <v>0.5877493536277286</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>0.2390220859642449</v>
+        <v>0.5358009711298616</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>9.875000999999999</v>
+        <v>4.6826925</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>0.0074367597462133</v>
-      </c>
-      <c r="M30" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.9802465124613901</v>
+      </c>
+      <c r="M30" s="19" t="n">
+        <v>-9.730978900874939</v>
       </c>
       <c r="N30" s="20" t="inlineStr">
         <is>
@@ -12128,28 +12070,28 @@
         </is>
       </c>
       <c r="O30" s="19" t="n">
-        <v>14.40111736061304</v>
+        <v>214.8679223530429</v>
       </c>
       <c r="P30" s="12" t="n">
-        <v>0.200456447318372</v>
+        <v>-7.475150278954917</v>
       </c>
       <c r="Q30" s="19" t="n">
-        <v>18.69378177551818</v>
+        <v>38.14057362285293</v>
       </c>
       <c r="R30" s="19" t="n">
-        <v>31.55704209289034</v>
+        <v>-8.347884944836451</v>
       </c>
       <c r="S30" s="21" t="n">
-        <v>0.5131200055934176</v>
+        <v>0.6458697123620912</v>
       </c>
       <c r="T30" s="15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U30" s="21" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>0.0072093763287943</v>
+        <v>3.055422759429443</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -12158,17 +12100,17 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>GLPGF</t>
+          <t>VTSYF</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Lakefront Biotherapeutics</t>
+          <t>Vitasoy International Holdings Limited</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -12177,7 +12119,7 @@
         </is>
       </c>
       <c r="F31" s="10" t="n">
-        <v>3189103616</v>
+        <v>803658432</v>
       </c>
       <c r="G31" s="17" t="inlineStr">
         <is>
@@ -12185,22 +12127,22 @@
         </is>
       </c>
       <c r="H31" s="18" t="n">
-        <v>0.881989217820347</v>
+        <v>0.8808517979838447</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>0.5877493536277286</v>
+        <v>0.5111983023788198</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>0.5358009711298616</v>
+        <v>0.2022806204753344</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>4.6826925</v>
+        <v>26.333334</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>0.9802465124613901</v>
+        <v>0.277008686396643</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>-9.730978900874939</v>
+        <v>69.75052804522805</v>
       </c>
       <c r="N31" s="20" t="inlineStr">
         <is>
@@ -12208,28 +12150,28 @@
         </is>
       </c>
       <c r="O31" s="19" t="n">
-        <v>214.8679223530429</v>
+        <v>14.19375766373652</v>
       </c>
       <c r="P31" s="12" t="n">
-        <v>-7.475150278954917</v>
+        <v>-0.7997894533258902</v>
       </c>
       <c r="Q31" s="19" t="n">
-        <v>38.14057362285293</v>
+        <v>15.01383812161213</v>
       </c>
       <c r="R31" s="19" t="n">
-        <v>-8.347884944836451</v>
+        <v>-30.5390929037204</v>
       </c>
       <c r="S31" s="21" t="n">
-        <v>0.6458697123620912</v>
+        <v>0.9897038473558776</v>
       </c>
       <c r="T31" s="15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U31" s="21" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>3.055422759429443</v>
+        <v>0.1325916317929503</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -12238,26 +12180,26 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>VTSYF</t>
+          <t>AKRTF</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Vitasoy International Holdings Limited</t>
+          <t>Aker Solutions ASA</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="F32" s="10" t="n">
-        <v>803658432</v>
+        <v>2162934272</v>
       </c>
       <c r="G32" s="17" t="inlineStr">
         <is>
@@ -12265,22 +12207,22 @@
         </is>
       </c>
       <c r="H32" s="18" t="n">
-        <v>0.8808517979838447</v>
+        <v>0.8756363829574741</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>0.5111983023788198</v>
+        <v>0.5740475914015073</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>0.2022806204753344</v>
+        <v>0.1002714467046379</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>26.333334</v>
+        <v>6.357143</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>0.277008686396643</v>
+        <v>0.1899476834987266</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>69.75052804522805</v>
+        <v>97.83006480559388</v>
       </c>
       <c r="N32" s="20" t="inlineStr">
         <is>
@@ -12288,28 +12230,28 @@
         </is>
       </c>
       <c r="O32" s="19" t="n">
-        <v>14.19375766373652</v>
+        <v>29.09419471425344</v>
       </c>
       <c r="P32" s="12" t="n">
-        <v>-0.7997894533258902</v>
+        <v>-0.5152563059397884</v>
       </c>
       <c r="Q32" s="19" t="n">
-        <v>15.01383812161213</v>
+        <v>7.903282852641389</v>
       </c>
       <c r="R32" s="19" t="n">
-        <v>-30.5390929037204</v>
+        <v>48.68024603713753</v>
       </c>
       <c r="S32" s="21" t="n">
-        <v>0.9897038473558776</v>
+        <v>0.6682729016026684</v>
       </c>
       <c r="T32" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U32" s="21" t="n">
         <v>1</v>
       </c>
       <c r="V32" s="12" t="n">
-        <v>0.1325916317929503</v>
+        <v>0.0347727447992026</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -12318,17 +12260,17 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>AKRTF</t>
+          <t>NXCLF</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Aker Solutions ASA</t>
+          <t>LIFULL Co., Ltd.</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -12337,7 +12279,7 @@
         </is>
       </c>
       <c r="F33" s="10" t="n">
-        <v>2162934272</v>
+        <v>202778128</v>
       </c>
       <c r="G33" s="17" t="inlineStr">
         <is>
@@ -12345,22 +12287,24 @@
         </is>
       </c>
       <c r="H33" s="18" t="n">
-        <v>0.8756363829574741</v>
+        <v>0.8725658703316487</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>0.5740475914015073</v>
+        <v>0.5358060628784111</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>0.1002714467046379</v>
+        <v>0.2390220859642449</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>6.357143</v>
+        <v>9.875000999999999</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>0.1899476834987266</v>
-      </c>
-      <c r="M33" s="19" t="n">
-        <v>97.83006480559388</v>
+        <v>0.0074367597462133</v>
+      </c>
+      <c r="M33" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N33" s="20" t="inlineStr">
         <is>
@@ -12368,28 +12312,28 @@
         </is>
       </c>
       <c r="O33" s="19" t="n">
-        <v>29.09419471425344</v>
+        <v>14.40111736061304</v>
       </c>
       <c r="P33" s="12" t="n">
-        <v>-0.5152563059397884</v>
+        <v>0.200456447318372</v>
       </c>
       <c r="Q33" s="19" t="n">
-        <v>7.903282852641389</v>
+        <v>18.69378177551818</v>
       </c>
       <c r="R33" s="19" t="n">
-        <v>48.68024603713753</v>
+        <v>31.55704209289034</v>
       </c>
       <c r="S33" s="21" t="n">
-        <v>0.6682729016026684</v>
+        <v>0.5131200055934176</v>
       </c>
       <c r="T33" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U33" s="21" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="V33" s="12" t="n">
-        <v>0.0347727447992026</v>
+        <v>0.0072093763287943</v>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
@@ -12833,7 +12777,7 @@
         </is>
       </c>
       <c r="H39" s="18" t="n">
-        <v>0.8425071504656739</v>
+        <v>0.8459009355632193</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>0.4713590413257659</v>
@@ -12876,7 +12820,7 @@
         <v>3</v>
       </c>
       <c r="U39" s="21" t="n">
-        <v>0.833</v>
+        <v>0.857</v>
       </c>
       <c r="V39" s="12" t="n">
         <v>0.0112918851891152</v>
@@ -13577,7 +13521,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Sweden  (SE)</t>
+          <t>Greece  (GR)</t>
         </is>
       </c>
     </row>
@@ -13652,19 +13596,19 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
           <t>1</t>
@@ -13672,7 +13616,7 @@
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>EVGGF</t>
+          <t>ATEK</t>
         </is>
       </c>
     </row>
@@ -13727,13 +13671,13 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="13" t="n">
-        <v>0.2554896906259428</v>
+        <v>0.2648396209839301</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.2554027856643192</v>
+        <v>0.2604063576671203</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>0.2554027856643192</v>
+        <v>0.2604063576671203</v>
       </c>
     </row>
     <row r="12">
@@ -13749,7 +13693,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>(EVGGF)</t>
+          <t>(ATEK)</t>
         </is>
       </c>
     </row>
@@ -13926,26 +13870,26 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>EVGGF</t>
+          <t>ATEK</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Evolution AB</t>
+          <t>Athena Technology Acquisition Corp. II Class A Com</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="F18" s="10" t="n">
-        <v>13701409792</v>
+        <v>93668928</v>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
@@ -13953,22 +13897,26 @@
         </is>
       </c>
       <c r="H18" s="18" t="n">
-        <v>0.2554027856643192</v>
+        <v>0.2604063576671203</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>0.2554896906259428</v>
+        <v>0.2648396209839301</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>9.251612127085345</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>11.8416395</v>
-      </c>
-      <c r="L18" s="12" t="n">
-        <v>3.186612254542723</v>
+        <v>-119.0342061320127</v>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L18" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M18" s="19" t="n">
-        <v>7.95169268374219</v>
+        <v>-0.9530193406291499</v>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
@@ -13976,28 +13924,30 @@
         </is>
       </c>
       <c r="O18" s="19" t="n">
-        <v>37.96901834887122</v>
+        <v>11.82962218892346</v>
       </c>
       <c r="P18" s="12" t="n">
-        <v>-0.705495866922169</v>
+        <v>-2.569826588301704</v>
       </c>
       <c r="Q18" s="19" t="n">
-        <v>66.65211948648924</v>
+        <v>0</v>
       </c>
       <c r="R18" s="19" t="n">
-        <v>-11.05011556697393</v>
+        <v>-5</v>
       </c>
       <c r="S18" s="21" t="n">
-        <v>0.4727575228325942</v>
+        <v>0.3791401584923105</v>
       </c>
       <c r="T18" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U18" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="12" t="n">
-        <v>6.450384366630369</v>
+        <v>0.333</v>
+      </c>
+      <c r="V18" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -14047,7 +13997,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Germany  (DE)</t>
+          <t>Sweden  (SE)</t>
         </is>
       </c>
     </row>
@@ -14142,7 +14092,7 @@
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>TELDF</t>
+          <t>EVGGF</t>
         </is>
       </c>
     </row>
@@ -14197,13 +14147,13 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="13" t="n">
-        <v>0.2531610358899512</v>
+        <v>0.2554896906259428</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.2134926875407663</v>
+        <v>0.2554027856643192</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>0.2134926875407663</v>
+        <v>0.2554027856643192</v>
       </c>
     </row>
     <row r="12">
@@ -14219,7 +14169,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>(TELDF)</t>
+          <t>(EVGGF)</t>
         </is>
       </c>
     </row>
@@ -14396,26 +14346,26 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>TELDF</t>
+          <t>EVGGF</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Telefonica Deutschland Holding AG</t>
+          <t>Evolution AB</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="F18" s="10" t="n">
-        <v>8359183360</v>
+        <v>13701409792</v>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
@@ -14423,22 +14373,22 @@
         </is>
       </c>
       <c r="H18" s="18" t="n">
-        <v>0.2134926875407663</v>
+        <v>0.2554027856643192</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>0.2531610358899512</v>
+        <v>0.2554896906259428</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>4.361218071197411</v>
+        <v>9.251612127085345</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>39.285713</v>
+        <v>11.8416395</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>1.513522245156618</v>
+        <v>3.186612254542723</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>11.89111372716676</v>
+        <v>7.95169268374219</v>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
@@ -14446,28 +14396,28 @@
         </is>
       </c>
       <c r="O18" s="19" t="n">
-        <v>4.61738564925211</v>
+        <v>37.96901834887122</v>
       </c>
       <c r="P18" s="12" t="n">
-        <v>0.2322006472491909</v>
+        <v>-0.705495866922169</v>
       </c>
       <c r="Q18" s="19" t="n">
-        <v>30.2496328928047</v>
+        <v>66.65211948648924</v>
       </c>
       <c r="R18" s="19" t="n">
-        <v>-15.24344768614329</v>
+        <v>-11.05011556697393</v>
       </c>
       <c r="S18" s="21" t="n">
-        <v>0.6287352381498974</v>
+        <v>0.4727575228325942</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>0</v>
       </c>
       <c r="U18" s="21" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>1.022905452765541</v>
+        <v>6.450384366630369</v>
       </c>
     </row>
   </sheetData>
@@ -14517,7 +14467,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Netherlands  (NL)</t>
+          <t>Germany  (DE)</t>
         </is>
       </c>
     </row>
@@ -14592,27 +14542,27 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>ICTSF</t>
+          <t>TELDF</t>
         </is>
       </c>
     </row>
@@ -14667,13 +14617,13 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="13" t="n">
-        <v>0.217137665599241</v>
+        <v>0.2531610358899512</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.1929802370832626</v>
+        <v>0.2134926875407663</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>0.1929802370832626</v>
+        <v>0.2134926875407663</v>
       </c>
     </row>
     <row r="12">
@@ -14689,7 +14639,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>(ICTSF)</t>
+          <t>(TELDF)</t>
         </is>
       </c>
     </row>
@@ -14866,26 +14816,26 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>ICTSF</t>
+          <t>TELDF</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>ICTS International N.V.</t>
+          <t>Telefonica Deutschland Holding AG</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="F18" s="10" t="n">
-        <v>215208320</v>
+        <v>8359183360</v>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
@@ -14893,26 +14843,22 @@
         </is>
       </c>
       <c r="H18" s="18" t="n">
-        <v>0.1929802370832626</v>
+        <v>0.2134926875407663</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>0.217137665599241</v>
+        <v>0.2531610358899512</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>-20.40639648544756</v>
-      </c>
-      <c r="K18" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L18" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.361218071197411</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>39.285713</v>
+      </c>
+      <c r="L18" s="12" t="n">
+        <v>1.513522245156618</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>-15.30145302932526</v>
+        <v>11.89111372716676</v>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
@@ -14920,30 +14866,28 @@
         </is>
       </c>
       <c r="O18" s="19" t="n">
-        <v>29.27165453598023</v>
-      </c>
-      <c r="P18" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.61738564925211</v>
+      </c>
+      <c r="P18" s="12" t="n">
+        <v>0.2322006472491909</v>
       </c>
       <c r="Q18" s="19" t="n">
-        <v>-2.86558528077608</v>
+        <v>30.2496328928047</v>
       </c>
       <c r="R18" s="19" t="n">
-        <v>56.25</v>
+        <v>-15.24344768614329</v>
       </c>
       <c r="S18" s="21" t="n">
-        <v>0.217166698678217</v>
+        <v>0.6287352381498974</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>0</v>
       </c>
       <c r="U18" s="21" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>0.4027282662395017</v>
+        <v>1.022905452765541</v>
       </c>
     </row>
   </sheetData>
@@ -14993,7 +14937,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Norway  (NO)</t>
+          <t>Netherlands  (NL)</t>
         </is>
       </c>
     </row>
@@ -15088,7 +15032,7 @@
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>TGSGY</t>
+          <t>ICTSF</t>
         </is>
       </c>
     </row>
@@ -15143,13 +15087,13 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="13" t="n">
-        <v>0.269019784424039</v>
+        <v>0.217137665599241</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.1843209443780383</v>
+        <v>0.1929802370832626</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>0.1843209443780383</v>
+        <v>0.1929802370832626</v>
       </c>
     </row>
     <row r="12">
@@ -15165,7 +15109,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>(TGSGY)</t>
+          <t>(ICTSF)</t>
         </is>
       </c>
     </row>
@@ -15342,26 +15286,26 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>TGSGY</t>
+          <t>ICTSF</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>TGS-NOPEC Geophysical Company ASA</t>
+          <t>ICTS International N.V.</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="F18" s="10" t="n">
-        <v>2715671296</v>
+        <v>215208320</v>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
@@ -15369,22 +15313,26 @@
         </is>
       </c>
       <c r="H18" s="18" t="n">
-        <v>0.1843209443780383</v>
+        <v>0.1929802370832626</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>0.269019784424039</v>
+        <v>0.217137665599241</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>4.237182715610314</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>30.530611</v>
-      </c>
-      <c r="L18" s="12" t="n">
-        <v>1.400480272291269</v>
+        <v>-20.40639648544756</v>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L18" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M18" s="19" t="n">
-        <v>11.59565962433768</v>
+        <v>-15.30145302932526</v>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
@@ -15392,28 +15340,28 @@
         </is>
       </c>
       <c r="O18" s="19" t="n">
-        <v>4.01051681513165</v>
+        <v>29.27165453598023</v>
       </c>
       <c r="P18" s="12" t="n">
-        <v>0.5398196367331386</v>
+        <v>3.152663371773751</v>
       </c>
       <c r="Q18" s="19" t="n">
-        <v>56.66474737296675</v>
+        <v>-2.86558528077608</v>
       </c>
       <c r="R18" s="19" t="n">
-        <v>79.8054687949769</v>
+        <v>56.25</v>
       </c>
       <c r="S18" s="21" t="n">
-        <v>0.6663596868845338</v>
+        <v>0.217166698678217</v>
       </c>
       <c r="T18" s="15" t="n">
         <v>0</v>
       </c>
       <c r="U18" s="21" t="n">
-        <v>0.556</v>
+        <v>0.75</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>1.954564053548294</v>
+        <v>0.4027282662395017</v>
       </c>
     </row>
   </sheetData>
@@ -15463,7 +15411,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Greece  (GR)</t>
+          <t>Norway  (NO)</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15506,7 @@
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>ATEK</t>
+          <t>TGSGY</t>
         </is>
       </c>
     </row>
@@ -15613,13 +15561,13 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="13" t="n">
-        <v>0.1872698919246121</v>
+        <v>0.269019784424039</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.1841351013705103</v>
+        <v>0.1843209443780383</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>0.1841351013705103</v>
+        <v>0.1843209443780383</v>
       </c>
     </row>
     <row r="12">
@@ -15635,7 +15583,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>(ATEK)</t>
+          <t>(TGSGY)</t>
         </is>
       </c>
     </row>
@@ -15812,26 +15760,26 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>ATEK</t>
+          <t>TGSGY</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Athena Technology Acquisition Corp. II Class A Com</t>
+          <t>TGS-NOPEC Geophysical Company ASA</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="F18" s="10" t="n">
-        <v>93668928</v>
+        <v>2715671296</v>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
@@ -15839,26 +15787,22 @@
         </is>
       </c>
       <c r="H18" s="18" t="n">
-        <v>0.1841351013705103</v>
+        <v>0.1843209443780383</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>0.1872698919246121</v>
+        <v>0.269019784424039</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>-119.0342061320127</v>
-      </c>
-      <c r="K18" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L18" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.237182715610314</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>30.530611</v>
+      </c>
+      <c r="L18" s="12" t="n">
+        <v>1.400480272291269</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>-0.9530193406291499</v>
+        <v>11.59565962433768</v>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
@@ -15866,32 +15810,28 @@
         </is>
       </c>
       <c r="O18" s="19" t="n">
-        <v>11.82962218892346</v>
-      </c>
-      <c r="P18" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.01051681513165</v>
+      </c>
+      <c r="P18" s="12" t="n">
+        <v>0.5398196367331386</v>
       </c>
       <c r="Q18" s="19" t="n">
+        <v>56.66474737296675</v>
+      </c>
+      <c r="R18" s="19" t="n">
+        <v>79.8054687949769</v>
+      </c>
+      <c r="S18" s="21" t="n">
+        <v>0.6663596868845338</v>
+      </c>
+      <c r="T18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="R18" s="19" t="n">
-        <v>-5</v>
-      </c>
-      <c r="S18" s="21" t="n">
-        <v>0.3791401584923105</v>
-      </c>
-      <c r="T18" s="15" t="n">
-        <v>3</v>
-      </c>
       <c r="U18" s="21" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="V18" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.556</v>
+      </c>
+      <c r="V18" s="12" t="n">
+        <v>1.954564053548294</v>
       </c>
     </row>
   </sheetData>
@@ -16411,7 +16351,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Iceland  (IS)</t>
+          <t>Argentina  (AR)</t>
         </is>
       </c>
     </row>
@@ -16486,19 +16426,19 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
           <t>1</t>
@@ -16506,7 +16446,7 @@
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>OSSFF</t>
+          <t>HGLD</t>
         </is>
       </c>
     </row>
@@ -16561,13 +16501,13 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="13" t="n">
-        <v>0.1435520246948516</v>
+        <v>0.1988130238655282</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.1217736937364642</v>
+        <v>0.171834096526976</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>0.1217736937364642</v>
+        <v>0.171834096526976</v>
       </c>
     </row>
     <row r="12">
@@ -16583,7 +16523,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>(OSSFF)</t>
+          <t>(HGLD)</t>
         </is>
       </c>
     </row>
@@ -16760,26 +16700,26 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>OSSFF</t>
+          <t>HGLD</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>√ñssur hf.</t>
+          <t>Patagonia Gold Corp.</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1767297920</v>
+        <v>155018000</v>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
@@ -16787,22 +16727,24 @@
         </is>
       </c>
       <c r="H18" s="18" t="n">
-        <v>0.1217736937364642</v>
+        <v>0.171834096526976</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>0.1435520246948516</v>
+        <v>0.1988130238655282</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>12.92026562878954</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>20.75</v>
+        <v>-100.7220637140637</v>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L18" s="12" t="n">
-        <v>1.965157875540967</v>
+        <v>10.11272750994846</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>3.72427304163861</v>
+        <v>-29.08113896450734</v>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
@@ -16810,28 +16752,28 @@
         </is>
       </c>
       <c r="O18" s="19" t="n">
-        <v>8.104889578870079</v>
+        <v>-8.241518350155371</v>
       </c>
       <c r="P18" s="12" t="n">
-        <v>1.614578400914687</v>
+        <v>-24.19774669774669</v>
       </c>
       <c r="Q18" s="19" t="n">
-        <v>18.73589457854136</v>
+        <v>-26.02892102335928</v>
       </c>
       <c r="R18" s="19" t="n">
-        <v>0</v>
+        <v>-8.33333333333333</v>
       </c>
       <c r="S18" s="21" t="n">
-        <v>0.4287912515873983</v>
+        <v>0.3456384156070175</v>
       </c>
       <c r="T18" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18" s="21" t="n">
-        <v>0.396</v>
+        <v>0.762</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>1.91205998117474</v>
+        <v>15.67580139548994</v>
       </c>
     </row>
   </sheetData>
@@ -16881,7 +16823,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Argentina  (AR)</t>
+          <t>Iceland  (IS)</t>
         </is>
       </c>
     </row>
@@ -16956,27 +16898,27 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>HGLD</t>
+          <t>OSSFF</t>
         </is>
       </c>
     </row>
@@ -17031,13 +16973,13 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="13" t="n">
-        <v>0.1405820373635179</v>
+        <v>0.1435520246948516</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.1215050548932885</v>
+        <v>0.1217736937364642</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>0.1215050548932885</v>
+        <v>0.1217736937364642</v>
       </c>
     </row>
     <row r="12">
@@ -17053,7 +16995,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>(HGLD)</t>
+          <t>(OSSFF)</t>
         </is>
       </c>
     </row>
@@ -17230,26 +17172,26 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>HGLD</t>
+          <t>OSSFF</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Patagonia Gold Corp.</t>
+          <t>√ñssur hf.</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="F18" s="10" t="n">
-        <v>155018000</v>
+        <v>1767297920</v>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
@@ -17257,24 +17199,22 @@
         </is>
       </c>
       <c r="H18" s="18" t="n">
-        <v>0.1215050548932885</v>
+        <v>0.1217736937364642</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>0.1405820373635179</v>
+        <v>0.1435520246948516</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>-100.7220637140637</v>
-      </c>
-      <c r="K18" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>12.92026562878954</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>20.75</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>10.11272750994846</v>
+        <v>1.965157875540967</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>-29.08113896450734</v>
+        <v>3.72427304163861</v>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
@@ -17282,30 +17222,28 @@
         </is>
       </c>
       <c r="O18" s="19" t="n">
-        <v>-8.241518350155371</v>
-      </c>
-      <c r="P18" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>8.104889578870079</v>
+      </c>
+      <c r="P18" s="12" t="n">
+        <v>1.614578400914687</v>
       </c>
       <c r="Q18" s="19" t="n">
-        <v>-26.02892102335928</v>
+        <v>18.73589457854136</v>
       </c>
       <c r="R18" s="19" t="n">
-        <v>-8.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="S18" s="21" t="n">
-        <v>0.3456384156070175</v>
+        <v>0.4287912515873983</v>
       </c>
       <c r="T18" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U18" s="21" t="n">
-        <v>0.762</v>
+        <v>0.396</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>15.67580139548994</v>
+        <v>1.91205998117474</v>
       </c>
     </row>
   </sheetData>
@@ -17981,10 +17919,10 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="13" t="n">
-        <v>0.3627121871241525</v>
+        <v>0.3697655774062279</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.4099799984019495</v>
+        <v>0.4170110576022009</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>0.8898346982480075</v>
@@ -18697,7 +18635,7 @@
         </is>
       </c>
       <c r="H24" s="18" t="n">
-        <v>0.6319212547491129</v>
+        <v>0.6154363524513101</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>0.4444773733040751</v>
@@ -18726,10 +18664,8 @@
       <c r="O24" s="19" t="n">
         <v>-17.14650145772594</v>
       </c>
-      <c r="P24" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P24" s="12" t="n">
+        <v>-1.215540648458713</v>
       </c>
       <c r="Q24" s="19" t="n">
         <v>-6.00253101451498</v>
@@ -18744,7 +18680,7 @@
         <v>3</v>
       </c>
       <c r="U24" s="21" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="V24" s="12" t="n">
         <v>0.08418421759055079</v>
@@ -19372,7 +19308,7 @@
         <v>0.0743726016603662</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>170.4574382380511</v>
+        <v>177.0135057887728</v>
       </c>
       <c r="N32" s="20" t="inlineStr">
         <is>
@@ -19517,7 +19453,7 @@
         </is>
       </c>
       <c r="H34" s="18" t="n">
-        <v>0.4155588978219694</v>
+        <v>0.418177049785846</v>
       </c>
       <c r="I34" s="12" t="n">
         <v>0.3330556532653451</v>
@@ -19560,7 +19496,7 @@
         <v>1</v>
       </c>
       <c r="U34" s="21" t="n">
-        <v>0.714</v>
+        <v>0.75</v>
       </c>
       <c r="V34" s="12" t="n">
         <v>0.0986404517693721</v>
@@ -19626,10 +19562,8 @@
       <c r="O35" s="19" t="n">
         <v>-12.09128726405409</v>
       </c>
-      <c r="P35" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P35" s="12" t="n">
+        <v>50.42761832829809</v>
       </c>
       <c r="Q35" s="19" t="n">
         <v>-0.16784201699073</v>
@@ -19736,12 +19670,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>CNPPF</t>
+          <t>LVSDF</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>China Overseas Property Holdings Limited</t>
+          <t>Lai Sun Development Company Limited</t>
         </is>
       </c>
       <c r="D37" s="16" t="inlineStr">
@@ -19751,11 +19685,11 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="F37" s="10" t="n">
-        <v>1413416704</v>
+        <v>72666440</v>
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
@@ -19763,22 +19697,26 @@
         </is>
       </c>
       <c r="H37" s="18" t="n">
-        <v>0.3806476725817262</v>
+        <v>0.3890338918097981</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>0.347986312062059</v>
+        <v>0.3455898342685965</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>0.7481833419198315</v>
-      </c>
-      <c r="K37" s="12" t="n">
-        <v>7.1733336</v>
+        <v>-19.55801728413084</v>
+      </c>
+      <c r="K37" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L37" s="12" t="n">
-        <v>0.2414250956490874</v>
-      </c>
-      <c r="M37" s="19" t="n">
-        <v>73.10123030780312</v>
+        <v>0.0032565287592644</v>
+      </c>
+      <c r="M37" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N37" s="20" t="inlineStr">
         <is>
@@ -19786,28 +19724,28 @@
         </is>
       </c>
       <c r="O37" s="19" t="n">
-        <v>31.47927493506227</v>
+        <v>-1.85296192132927</v>
       </c>
       <c r="P37" s="12" t="n">
-        <v>0.0229064509574116</v>
+        <v>-15.62224849229418</v>
       </c>
       <c r="Q37" s="19" t="n">
-        <v>13.02682356017642</v>
+        <v>-29.92619342405965</v>
       </c>
       <c r="R37" s="19" t="n">
-        <v>-9.3096550133858</v>
+        <v>0</v>
       </c>
       <c r="S37" s="21" t="n">
-        <v>0.7654419531683365</v>
+        <v>0.6749999999999999</v>
       </c>
       <c r="T37" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37" s="21" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="V37" s="12" t="n">
-        <v>0.0944805409084075</v>
+        <v>0.0148340786120158</v>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
@@ -19816,26 +19754,26 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>FPAFF</t>
+          <t>GEAHF</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>First Pacific Company Ltd.</t>
+          <t>Great Eagle Holdings Limited</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="F38" s="10" t="n">
-        <v>2727756800</v>
+        <v>1649336448</v>
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
@@ -19843,22 +19781,26 @@
         </is>
       </c>
       <c r="H38" s="18" t="n">
-        <v>0.3762128280216591</v>
+        <v>0.3814323173296215</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>0.3686179861874262</v>
+        <v>0.3724982614988312</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>5.773126231943388</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <v>4.2666664</v>
+        <v>-126.4699839383523</v>
+      </c>
+      <c r="K38" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L38" s="12" t="n">
-        <v>0.6215267954794021</v>
-      </c>
-      <c r="M38" s="19" t="n">
-        <v>13.19032547183092</v>
+        <v>0.0316644530644803</v>
+      </c>
+      <c r="M38" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
@@ -19866,28 +19808,28 @@
         </is>
       </c>
       <c r="O38" s="19" t="n">
-        <v>18.67861618860696</v>
+        <v>3.41751950319312</v>
       </c>
       <c r="P38" s="12" t="n">
-        <v>2.821393063921867</v>
+        <v>-81.15407773958373</v>
       </c>
       <c r="Q38" s="19" t="n">
-        <v>33.42096261910579</v>
+        <v>-1.34666867499512</v>
       </c>
       <c r="R38" s="19" t="n">
-        <v>-14.66666857401529</v>
+        <v>30.177513206837</v>
       </c>
       <c r="S38" s="21" t="n">
-        <v>0.8604128707443203</v>
+        <v>0.4807875899847338</v>
       </c>
       <c r="T38" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U38" s="21" t="n">
-        <v>1</v>
+        <v>0.429</v>
       </c>
       <c r="V38" s="12" t="n">
-        <v>0.2665777473735646</v>
+        <v>0.0839009454557219</v>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
@@ -19896,17 +19838,17 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>BJWTF</t>
+          <t>CNPPF</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Beijing Enterprises Water Group Limited</t>
+          <t>China Overseas Property Holdings Limited</t>
         </is>
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -19915,7 +19857,7 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>3008433408</v>
+        <v>1413416704</v>
       </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
@@ -19923,22 +19865,22 @@
         </is>
       </c>
       <c r="H39" s="18" t="n">
-        <v>0.3701122343904206</v>
+        <v>0.3806476725817262</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>0.3068318013615241</v>
+        <v>0.347986312062059</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>12.94899763296724</v>
+        <v>0.7481833419198315</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>15.000001</v>
+        <v>7.1733336</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>0.0850324005914327</v>
+        <v>0.2414250956490874</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>153.1660959403892</v>
+        <v>73.10123030780312</v>
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
@@ -19946,28 +19888,28 @@
         </is>
       </c>
       <c r="O39" s="19" t="n">
-        <v>4.58077285923901</v>
+        <v>31.47927493506227</v>
       </c>
       <c r="P39" s="12" t="n">
-        <v>9.089482956389167</v>
+        <v>0.0229064509574116</v>
       </c>
       <c r="Q39" s="19" t="n">
-        <v>33.00726660786611</v>
+        <v>13.02682356017642</v>
       </c>
       <c r="R39" s="19" t="n">
-        <v>-3.53697040504711</v>
+        <v>-9.3096550133858</v>
       </c>
       <c r="S39" s="21" t="n">
-        <v>0.6697813792511728</v>
+        <v>0.7654419531683365</v>
       </c>
       <c r="T39" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="U39" s="21" t="n">
-        <v>0.444</v>
-      </c>
       <c r="V39" s="12" t="n">
-        <v>0.1363617449631271</v>
+        <v>0.0944805409084075</v>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
@@ -19976,17 +19918,17 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>DGTLF</t>
+          <t>FPAFF</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>OCI International Holdings Limited</t>
+          <t>First Pacific Company Ltd.</t>
         </is>
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -19995,7 +19937,7 @@
         </is>
       </c>
       <c r="F40" s="10" t="n">
-        <v>53841028</v>
+        <v>2727756800</v>
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
@@ -20003,24 +19945,22 @@
         </is>
       </c>
       <c r="H40" s="18" t="n">
-        <v>0.3697805819169872</v>
+        <v>0.3762128280216591</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>0.2783828276565172</v>
+        <v>0.3686179861874262</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>10.74906139065299</v>
-      </c>
-      <c r="K40" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.773126231943388</v>
+      </c>
+      <c r="K40" s="12" t="n">
+        <v>4.2666664</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>0.212196443491558</v>
+        <v>0.6215267954794021</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>-105.5106154362432</v>
+        <v>13.19032547183092</v>
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
@@ -20028,30 +19968,28 @@
         </is>
       </c>
       <c r="O40" s="19" t="n">
-        <v>-32.60007956269983</v>
-      </c>
-      <c r="P40" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>18.67861618860696</v>
+      </c>
+      <c r="P40" s="12" t="n">
+        <v>2.821393063921867</v>
       </c>
       <c r="Q40" s="19" t="n">
-        <v>-18.74198864676799</v>
+        <v>33.42096261910579</v>
       </c>
       <c r="R40" s="19" t="n">
-        <v>-33.33333793245704</v>
+        <v>-14.66666857401529</v>
       </c>
       <c r="S40" s="21" t="n">
-        <v>0.4</v>
+        <v>0.8604128707443203</v>
       </c>
       <c r="T40" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="U40" s="21" t="n">
-        <v>0.5</v>
-      </c>
       <c r="V40" s="12" t="n">
-        <v>0.821599035585668</v>
+        <v>0.2665777473735646</v>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
@@ -20060,17 +19998,17 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>CMHHY</t>
+          <t>BJWTF</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>China Merchants Port Holdings Company Limited</t>
+          <t>Beijing Enterprises Water Group Limited</t>
         </is>
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -20079,7 +20017,7 @@
         </is>
       </c>
       <c r="F41" s="10" t="n">
-        <v>6981288960</v>
+        <v>3008433408</v>
       </c>
       <c r="G41" s="17" t="inlineStr">
         <is>
@@ -20087,22 +20025,22 @@
         </is>
       </c>
       <c r="H41" s="18" t="n">
-        <v>0.3613744908840556</v>
+        <v>0.3701122343904206</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>0.3171725333053786</v>
+        <v>0.3068318013615241</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>3.743454930514535</v>
+        <v>12.94899763296724</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>8.484693999999999</v>
+        <v>15.000001</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>0.0632345947121002</v>
+        <v>0.0850324005914327</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>123.1720968616088</v>
+        <v>164.1065433342761</v>
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
@@ -20110,28 +20048,28 @@
         </is>
       </c>
       <c r="O41" s="19" t="n">
-        <v>3.8978886756238</v>
+        <v>4.58077285923901</v>
       </c>
       <c r="P41" s="12" t="n">
-        <v>1.790144567076014</v>
+        <v>9.089482956389167</v>
       </c>
       <c r="Q41" s="19" t="n">
-        <v>96.34566422045829</v>
+        <v>33.00726660786611</v>
       </c>
       <c r="R41" s="19" t="n">
-        <v>-0.05381949937204</v>
+        <v>-3.53697040504711</v>
       </c>
       <c r="S41" s="21" t="n">
-        <v>0.6196239921265492</v>
+        <v>0.6697813792511728</v>
       </c>
       <c r="T41" s="15" t="n">
         <v>1</v>
       </c>
       <c r="U41" s="21" t="n">
-        <v>1</v>
+        <v>0.444</v>
       </c>
       <c r="V41" s="12" t="n">
-        <v>0.5227863531526135</v>
+        <v>0.1363617449631271</v>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
@@ -20140,26 +20078,26 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>CPWIF</t>
+          <t>DGTLF</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>China Power International Development Limited</t>
+          <t>OCI International Holdings Limited</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="F42" s="10" t="n">
-        <v>5392148992</v>
+        <v>53841028</v>
       </c>
       <c r="G42" s="17" t="inlineStr">
         <is>
@@ -20167,22 +20105,24 @@
         </is>
       </c>
       <c r="H42" s="18" t="n">
-        <v>0.3610455563886895</v>
+        <v>0.3697805819169872</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>0.3272802763193653</v>
+        <v>0.2783828276565172</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>9.354477811348344</v>
-      </c>
-      <c r="K42" s="12" t="n">
-        <v>10.8975</v>
+        <v>10.74906139065299</v>
+      </c>
+      <c r="K42" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L42" s="12" t="n">
-        <v>0.0919566767775287</v>
+        <v>0.212196443491558</v>
       </c>
       <c r="M42" s="19" t="n">
-        <v>-37.09161232316334</v>
+        <v>-105.5106154362432</v>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
@@ -20190,28 +20130,28 @@
         </is>
       </c>
       <c r="O42" s="19" t="n">
-        <v>3.55463318097399</v>
+        <v>-32.60007956269983</v>
       </c>
       <c r="P42" s="12" t="n">
-        <v>7.063155655766342</v>
+        <v>15.13279596156978</v>
       </c>
       <c r="Q42" s="19" t="n">
-        <v>57.45697092027876</v>
+        <v>-18.74198864676799</v>
       </c>
       <c r="R42" s="19" t="n">
-        <v>0</v>
+        <v>-33.33333793245704</v>
       </c>
       <c r="S42" s="21" t="n">
-        <v>0.46777316590487</v>
+        <v>0.4</v>
       </c>
       <c r="T42" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U42" s="21" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="V42" s="12" t="n">
-        <v>0.1099777379146688</v>
+        <v>0.821599035585668</v>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
@@ -20220,26 +20160,26 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>FESTF</t>
+          <t>CMHHY</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Hybrid Kinetic Group Limited</t>
+          <t>China Merchants Port Holdings Company Limited</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="F43" s="10" t="n">
-        <v>101764360</v>
+        <v>6981288960</v>
       </c>
       <c r="G43" s="17" t="inlineStr">
         <is>
@@ -20247,26 +20187,22 @@
         </is>
       </c>
       <c r="H43" s="18" t="n">
-        <v>0.3546606348731874</v>
+        <v>0.3613744908840556</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>0.3482992371995509</v>
+        <v>0.3171725333053786</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>11.04067506027324</v>
-      </c>
-      <c r="K43" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L43" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>3.743454930514535</v>
+      </c>
+      <c r="K43" s="12" t="n">
+        <v>8.484693999999999</v>
+      </c>
+      <c r="L43" s="12" t="n">
+        <v>0.0632345947121002</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>11.82732343622069</v>
+        <v>102.4175900452689</v>
       </c>
       <c r="N43" s="20" t="inlineStr">
         <is>
@@ -20274,28 +20210,28 @@
         </is>
       </c>
       <c r="O43" s="19" t="n">
-        <v>-9.580684464852581</v>
+        <v>3.8978886756238</v>
       </c>
       <c r="P43" s="12" t="n">
-        <v>-0.9731449236538976</v>
+        <v>1.790144567076014</v>
       </c>
       <c r="Q43" s="19" t="n">
-        <v>26.86674583468278</v>
+        <v>96.34566422045829</v>
       </c>
       <c r="R43" s="19" t="n">
-        <v>0</v>
+        <v>-0.05381949937204</v>
       </c>
       <c r="S43" s="21" t="n">
-        <v>0.7795472655793105</v>
+        <v>0.6196239921265492</v>
       </c>
       <c r="T43" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U43" s="21" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="V43" s="12" t="n">
-        <v>1.831018748425636</v>
+        <v>0.5227863531526135</v>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
@@ -20304,26 +20240,26 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>CESTF</t>
+          <t>CPWIF</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Chinese Estates Holdings Limited</t>
+          <t>China Power International Development Limited</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>247418208</v>
+        <v>5392148992</v>
       </c>
       <c r="G44" s="17" t="inlineStr">
         <is>
@@ -20331,24 +20267,22 @@
         </is>
       </c>
       <c r="H44" s="18" t="n">
-        <v>0.3514635970608777</v>
+        <v>0.3610455563886895</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>0.3378061226580183</v>
+        <v>0.3272802763193653</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>-10.03452573894578</v>
-      </c>
-      <c r="K44" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>9.354477811348344</v>
+      </c>
+      <c r="K44" s="12" t="n">
+        <v>10.8975</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>0.0207730924123005</v>
+        <v>0.0919566767775287</v>
       </c>
       <c r="M44" s="19" t="n">
-        <v>-113.253184664566</v>
+        <v>-37.09161232316334</v>
       </c>
       <c r="N44" s="20" t="inlineStr">
         <is>
@@ -20356,30 +20290,28 @@
         </is>
       </c>
       <c r="O44" s="19" t="n">
-        <v>-0.10428431809179</v>
-      </c>
-      <c r="P44" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>3.55463318097399</v>
+      </c>
+      <c r="P44" s="12" t="n">
+        <v>7.063155655766342</v>
       </c>
       <c r="Q44" s="19" t="n">
-        <v>-67.88195828351269</v>
+        <v>57.45697092027876</v>
       </c>
       <c r="R44" s="19" t="n">
         <v>0</v>
       </c>
       <c r="S44" s="21" t="n">
-        <v>0.4370874455578947</v>
+        <v>0.46777316590487</v>
       </c>
       <c r="T44" s="15" t="n">
         <v>3</v>
       </c>
       <c r="U44" s="21" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="V44" s="12" t="n">
-        <v>0.8217689916301315</v>
+        <v>0.1099777379146688</v>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
@@ -20388,26 +20320,26 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>CGHLY</t>
+          <t>FESTF</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>China Gas Holdings Ltd.</t>
+          <t>Hybrid Kinetic Group Limited</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="F45" s="10" t="n">
-        <v>3747675392</v>
+        <v>101764360</v>
       </c>
       <c r="G45" s="17" t="inlineStr">
         <is>
@@ -20415,22 +20347,26 @@
         </is>
       </c>
       <c r="H45" s="18" t="n">
-        <v>0.342118189021945</v>
+        <v>0.3546606348731874</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>0.291787084348739</v>
+        <v>0.3482992371995509</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>6.551234910918546</v>
-      </c>
-      <c r="K45" s="12" t="n">
-        <v>10.815723</v>
-      </c>
-      <c r="L45" s="12" t="n">
-        <v>0.0668892478161258</v>
+        <v>11.04067506027324</v>
+      </c>
+      <c r="K45" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L45" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M45" s="19" t="n">
-        <v>47.12865483948509</v>
+        <v>11.82732343622069</v>
       </c>
       <c r="N45" s="20" t="inlineStr">
         <is>
@@ -20438,28 +20374,28 @@
         </is>
       </c>
       <c r="O45" s="19" t="n">
-        <v>5.76847656985159</v>
+        <v>-9.580684464852581</v>
       </c>
       <c r="P45" s="12" t="n">
-        <v>5.015703557848574</v>
+        <v>-0.9731449236538976</v>
       </c>
       <c r="Q45" s="19" t="n">
-        <v>12.61801946097333</v>
+        <v>26.86674583468278</v>
       </c>
       <c r="R45" s="19" t="n">
-        <v>-31.21199798583984</v>
+        <v>0</v>
       </c>
       <c r="S45" s="21" t="n">
-        <v>0.8174277178977543</v>
+        <v>0.7795472655793105</v>
       </c>
       <c r="T45" s="15" t="n">
         <v>2</v>
       </c>
       <c r="U45" s="21" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="V45" s="12" t="n">
-        <v>0.0472845008256515</v>
+        <v>1.831018748425636</v>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
@@ -20468,12 +20404,12 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>CAOVF</t>
+          <t>CESTF</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>China Overseas Land &amp; Investment Limited</t>
+          <t>Chinese Estates Holdings Limited</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
@@ -20483,11 +20419,11 @@
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="F46" s="10" t="n">
-        <v>18059057152</v>
+        <v>247418208</v>
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
@@ -20495,22 +20431,24 @@
         </is>
       </c>
       <c r="H46" s="18" t="n">
-        <v>0.336901238458868</v>
+        <v>0.3514635970608777</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>0.2984522483973129</v>
+        <v>0.3378061226580183</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>8.998290529135975</v>
-      </c>
-      <c r="K46" s="12" t="n">
-        <v>9.705882000000001</v>
+        <v>-10.03452573894578</v>
+      </c>
+      <c r="K46" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L46" s="12" t="n">
-        <v>0.0465502260966634</v>
+        <v>0.0207730924123005</v>
       </c>
       <c r="M46" s="19" t="n">
-        <v>91.40805004967736</v>
+        <v>-113.253184664566</v>
       </c>
       <c r="N46" s="20" t="inlineStr">
         <is>
@@ -20518,28 +20456,28 @@
         </is>
       </c>
       <c r="O46" s="19" t="n">
-        <v>3.37726761052638</v>
+        <v>-0.10428431809179</v>
       </c>
       <c r="P46" s="12" t="n">
-        <v>6.637357871334608</v>
+        <v>-10.11790350280606</v>
       </c>
       <c r="Q46" s="19" t="n">
-        <v>12.88450242346655</v>
+        <v>-67.88195828351269</v>
       </c>
       <c r="R46" s="19" t="n">
-        <v>9.27152229000572</v>
+        <v>0</v>
       </c>
       <c r="S46" s="21" t="n">
-        <v>0.5857744164156171</v>
+        <v>0.4370874455578947</v>
       </c>
       <c r="T46" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U46" s="21" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="V46" s="12" t="n">
-        <v>0.1074376217351588</v>
+        <v>0.8217689916301315</v>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
@@ -20548,12 +20486,12 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>HKCVF</t>
+          <t>CGHLY</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>HK Electric Investments and HK Electric Investment</t>
+          <t>China Gas Holdings Ltd.</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
@@ -20563,11 +20501,11 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="F47" s="10" t="n">
-        <v>5920254464</v>
+        <v>3747675392</v>
       </c>
       <c r="G47" s="17" t="inlineStr">
         <is>
@@ -20575,22 +20513,22 @@
         </is>
       </c>
       <c r="H47" s="18" t="n">
-        <v>0.3170811388818329</v>
+        <v>0.342118189021945</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>0.3431779752068338</v>
+        <v>0.291787084348739</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>6.435059664763645</v>
+        <v>6.551234910918546</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>13.400001</v>
+        <v>10.815723</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>0.1220318766541616</v>
+        <v>0.0668892478161258</v>
       </c>
       <c r="M47" s="19" t="n">
-        <v>44.01837819381947</v>
+        <v>47.12865483948509</v>
       </c>
       <c r="N47" s="20" t="inlineStr">
         <is>
@@ -20598,28 +20536,28 @@
         </is>
       </c>
       <c r="O47" s="19" t="n">
-        <v>5.53992208858667</v>
+        <v>5.76847656985159</v>
       </c>
       <c r="P47" s="12" t="n">
-        <v>5.862183146837177</v>
+        <v>5.015703557848574</v>
       </c>
       <c r="Q47" s="19" t="n">
-        <v>72.63830140167538</v>
+        <v>12.61801946097333</v>
       </c>
       <c r="R47" s="19" t="n">
-        <v>72.68940476901922</v>
+        <v>-31.21199798583984</v>
       </c>
       <c r="S47" s="21" t="n">
-        <v>0.6481283048145774</v>
+        <v>0.8174277178977543</v>
       </c>
       <c r="T47" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U47" s="21" t="n">
-        <v>0.889</v>
+        <v>1</v>
       </c>
       <c r="V47" s="12" t="n">
-        <v>0.4910221832960106</v>
+        <v>0.0472845008256515</v>
       </c>
     </row>
   </sheetData>
@@ -20819,10 +20757,10 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="13" t="n">
-        <v>0.3635159371727587</v>
+        <v>0.369706687779425</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.4789053715149756</v>
+        <v>0.4853448848870114</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>0.8647152962908655</v>
@@ -21232,10 +21170,8 @@
       <c r="O20" s="19" t="n">
         <v>-1.00627227152373</v>
       </c>
-      <c r="P20" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P20" s="12" t="n">
+        <v>100.021978021978</v>
       </c>
       <c r="Q20" s="19" t="n">
         <v>-2.32788521584727</v>
@@ -21642,7 +21578,7 @@
         <v>0.0564137478309782</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>181.3745532466584</v>
+        <v>150.3547617312737</v>
       </c>
       <c r="N25" s="20" t="inlineStr">
         <is>
@@ -22162,10 +22098,8 @@
       <c r="O31" s="19" t="n">
         <v>-0.79987309232041</v>
       </c>
-      <c r="P31" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P31" s="12" t="n">
+        <v>66.6530382167423</v>
       </c>
       <c r="Q31" s="19" t="n">
         <v>-4.08517098207571</v>
@@ -22315,8 +22249,10 @@
       <c r="L33" s="12" t="n">
         <v>0.0411255055221494</v>
       </c>
-      <c r="M33" s="19" t="n">
-        <v>179.3336839072449</v>
+      <c r="M33" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N33" s="20" t="inlineStr">
         <is>
@@ -22396,7 +22332,7 @@
         <v>0.09430482265357561</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>133.1144372630552</v>
+        <v>128.4437509338955</v>
       </c>
       <c r="N34" s="20" t="inlineStr">
         <is>
@@ -22541,10 +22477,10 @@
         </is>
       </c>
       <c r="H36" s="18" t="n">
-        <v>0.2833080469509478</v>
+        <v>0.3379284233307807</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>0.2661883849121965</v>
+        <v>0.3260128592452229</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>-6.716231003605071</v>
@@ -22570,10 +22506,8 @@
       <c r="O36" s="19" t="n">
         <v>-11.45720100366977</v>
       </c>
-      <c r="P36" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P36" s="12" t="n">
+        <v>-4.565670426793814</v>
       </c>
       <c r="Q36" s="19" t="n">
         <v>-14.68975390092488</v>
@@ -22588,7 +22522,7 @@
         <v>2</v>
       </c>
       <c r="U36" s="21" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="V36" s="12" t="n">
         <v>0.0705885058099608</v>
@@ -22600,12 +22534,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>TMPPF</t>
+          <t>BEIJF</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Times China Holdings Limited</t>
+          <t>Beijing North Star Company Limited</t>
         </is>
       </c>
       <c r="D37" s="16" t="inlineStr">
@@ -22615,11 +22549,11 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="F37" s="10" t="n">
-        <v>149618384</v>
+        <v>416163680</v>
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
@@ -22627,28 +22561,24 @@
         </is>
       </c>
       <c r="H37" s="18" t="n">
-        <v>0.2409578766808694</v>
+        <v>0.3164580711998925</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>0.2899408751464443</v>
+        <v>0.3030235407515213</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>20.53511824013563</v>
+        <v>-12.63822575011578</v>
       </c>
       <c r="K37" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="L37" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M37" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L37" s="12" t="n">
+        <v>0.0635211818485891</v>
+      </c>
+      <c r="M37" s="19" t="n">
+        <v>116.225273430877</v>
       </c>
       <c r="N37" s="20" t="inlineStr">
         <is>
@@ -22656,28 +22586,28 @@
         </is>
       </c>
       <c r="O37" s="19" t="n">
-        <v>-7.80002959293858</v>
+        <v>1.50339276526475</v>
       </c>
       <c r="P37" s="12" t="n">
-        <v>14.87894469461496</v>
+        <v>-7.296717523563864</v>
       </c>
       <c r="Q37" s="19" t="n">
-        <v>59.57350028473905</v>
+        <v>-26.59690135858478</v>
       </c>
       <c r="R37" s="19" t="n">
         <v>0</v>
       </c>
       <c r="S37" s="21" t="n">
-        <v>0.7058823529411764</v>
+        <v>0.6825169638263237</v>
       </c>
       <c r="T37" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U37" s="21" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="V37" s="12" t="n">
-        <v>0.0446563921829875</v>
+        <v>0.06941957000889031</v>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
@@ -22686,17 +22616,17 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>CSDXF</t>
+          <t>TMPPF</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>COSCO SHIPPING Energy Transportation Co., Ltd. Cla</t>
+          <t>Times China Holdings Limited</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -22705,7 +22635,7 @@
         </is>
       </c>
       <c r="F38" s="10" t="n">
-        <v>9564136448</v>
+        <v>149618384</v>
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
@@ -22713,22 +22643,28 @@
         </is>
       </c>
       <c r="H38" s="18" t="n">
-        <v>0.2368307183009382</v>
+        <v>0.2482742340273612</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>0.3042042610208102</v>
+        <v>0.2899408751464443</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>3.020104954776236</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <v>14.583334</v>
-      </c>
-      <c r="L38" s="12" t="n">
-        <v>0.2061006128151808</v>
-      </c>
-      <c r="M38" s="19" t="n">
-        <v>18.33944977193198</v>
+        <v>20.53511824013563</v>
+      </c>
+      <c r="K38" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L38" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M38" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
@@ -22736,28 +22672,28 @@
         </is>
       </c>
       <c r="O38" s="19" t="n">
-        <v>7.39413475628362</v>
+        <v>-7.80002959293858</v>
       </c>
       <c r="P38" s="12" t="n">
-        <v>1.903560029001738</v>
+        <v>14.87894469461496</v>
       </c>
       <c r="Q38" s="19" t="n">
-        <v>44.98291342676316</v>
+        <v>59.57350028473905</v>
       </c>
       <c r="R38" s="19" t="n">
-        <v>124.0716977463034</v>
+        <v>0</v>
       </c>
       <c r="S38" s="21" t="n">
-        <v>0.6413819717533299</v>
+        <v>0.7058823529411764</v>
       </c>
       <c r="T38" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U38" s="21" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="V38" s="12" t="n">
-        <v>0.4035319106743975</v>
+        <v>0.0446563921829875</v>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
@@ -22766,26 +22702,26 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>BEIJF</t>
+          <t>CSDXF</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Beijing North Star Company Limited</t>
+          <t>COSCO SHIPPING Energy Transportation Co., Ltd. Cla</t>
         </is>
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>416163680</v>
+        <v>9564136448</v>
       </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
@@ -22793,24 +22729,22 @@
         </is>
       </c>
       <c r="H39" s="18" t="n">
-        <v>0.2237696481066592</v>
+        <v>0.2368307183009382</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>0.2142700005245588</v>
+        <v>0.3042042610208102</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>-12.63822575011578</v>
-      </c>
-      <c r="K39" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>3.020104954776236</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>14.583334</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>0.0635211818485891</v>
+        <v>0.2061006128151808</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>116.225273430877</v>
+        <v>18.33944977193198</v>
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
@@ -22818,30 +22752,28 @@
         </is>
       </c>
       <c r="O39" s="19" t="n">
-        <v>1.50339276526475</v>
-      </c>
-      <c r="P39" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>7.39413475628362</v>
+      </c>
+      <c r="P39" s="12" t="n">
+        <v>1.903560029001738</v>
       </c>
       <c r="Q39" s="19" t="n">
-        <v>-26.59690135858478</v>
+        <v>44.98291342676316</v>
       </c>
       <c r="R39" s="19" t="n">
-        <v>0</v>
+        <v>124.0716977463034</v>
       </c>
       <c r="S39" s="21" t="n">
-        <v>0.6825169638263237</v>
+        <v>0.6413819717533299</v>
       </c>
       <c r="T39" s="15" t="n">
         <v>2</v>
       </c>
       <c r="U39" s="21" t="n">
-        <v>0.571</v>
+        <v>1</v>
       </c>
       <c r="V39" s="12" t="n">
-        <v>0.06941957000889031</v>
+        <v>0.4035319106743975</v>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
@@ -22877,7 +22809,7 @@
         </is>
       </c>
       <c r="H40" s="18" t="n">
-        <v>0.2128930441570624</v>
+        <v>0.2128162082663624</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>0.2041985709521816</v>
@@ -22920,7 +22852,7 @@
         <v>0</v>
       </c>
       <c r="U40" s="21" t="n">
-        <v>0.375</v>
+        <v>0.373</v>
       </c>
       <c r="V40" s="12" t="n">
         <v>0.0606040715448017</v>
@@ -24401,13 +24333,13 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="13" t="n">
-        <v>0.3492667197119335</v>
+        <v>0.3542910015674186</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.4554161242051632</v>
+        <v>0.4584468713770132</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>0.7746323141100037</v>
+        <v>0.7852735723144277</v>
       </c>
     </row>
     <row r="12">
@@ -24627,7 +24559,7 @@
         </is>
       </c>
       <c r="H18" s="18" t="n">
-        <v>0.7746323141100037</v>
+        <v>0.7852735723144277</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>0.4671930834167982</v>
@@ -24676,7 +24608,7 @@
         <v>3</v>
       </c>
       <c r="U18" s="21" t="n">
-        <v>0.667</v>
+        <v>0.75</v>
       </c>
       <c r="V18" s="12" t="n">
         <v>0.0128709928618744</v>
@@ -25028,17 +24960,17 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>MDNDF</t>
+          <t>TDHOY</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>McDonald's Holdings Company (Japan), Ltd.</t>
+          <t>T&amp;D Holdings, Inc.</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -25047,7 +24979,7 @@
         </is>
       </c>
       <c r="F23" s="10" t="n">
-        <v>5469922304</v>
+        <v>14424766464</v>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
@@ -25055,51 +24987,59 @@
         </is>
       </c>
       <c r="H23" s="18" t="n">
-        <v>0.6427034930424186</v>
+        <v>0.6431629903290214</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>0.4655873018304962</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>-0.9874461489702584</v>
+        <v>0.409217877329693</v>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K23" s="12" t="n">
-        <v>25.085365</v>
+        <v>17.476744</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>0.0195028391973415</v>
-      </c>
-      <c r="M23" s="19" t="n">
-        <v>195.1157813023242</v>
+        <v>0.008947678009880101</v>
+      </c>
+      <c r="M23" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O23" s="19" t="n">
-        <v>25.70341985115973</v>
-      </c>
-      <c r="P23" s="12" t="n">
-        <v>-1.067115266975444</v>
+      <c r="O23" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P23" s="20" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q23" s="19" t="n">
-        <v>16.48047777014992</v>
+        <v>4.759</v>
       </c>
       <c r="R23" s="19" t="n">
-        <v>36.32718580063827</v>
+        <v>38.21942485376493</v>
       </c>
       <c r="S23" s="21" t="n">
-        <v>0.7048436297129206</v>
+        <v>0.6155205882352941</v>
       </c>
       <c r="T23" s="15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U23" s="21" t="n">
-        <v>0.667</v>
+        <v>0.75</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>0.013129851282519</v>
+        <v>0.0052923852493239</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -25108,26 +25048,26 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>JPXGY</t>
+          <t>MDNDF</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Japan Exchange Group, Inc.</t>
+          <t>McDonald's Holdings Company (Japan), Ltd.</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="F24" s="10" t="n">
-        <v>14020936704</v>
+        <v>5469922304</v>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
@@ -25135,24 +25075,22 @@
         </is>
       </c>
       <c r="H24" s="18" t="n">
-        <v>0.6395979536579929</v>
+        <v>0.6427034930424186</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>0.3824722514294422</v>
+        <v>0.4655873018304962</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>-1.916853128246724</v>
+        <v>-0.9874461489702584</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>37.88889</v>
+        <v>25.085365</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>0.0406386293465501</v>
-      </c>
-      <c r="M24" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.0195028391973415</v>
+      </c>
+      <c r="M24" s="19" t="n">
+        <v>195.1157813023242</v>
       </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
@@ -25160,28 +25098,28 @@
         </is>
       </c>
       <c r="O24" s="19" t="n">
-        <v>72.41255984458697</v>
+        <v>25.70341985115973</v>
       </c>
       <c r="P24" s="12" t="n">
-        <v>-2.046085497815548</v>
+        <v>-1.067115266975444</v>
       </c>
       <c r="Q24" s="19" t="n">
-        <v>66.08556879370417</v>
+        <v>16.48047777014992</v>
       </c>
       <c r="R24" s="19" t="n">
-        <v>35.38156234723725</v>
+        <v>36.32718580063827</v>
       </c>
       <c r="S24" s="21" t="n">
-        <v>0.6566123519161398</v>
+        <v>0.7048436297129206</v>
       </c>
       <c r="T24" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" s="21" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>0.0854039464951392</v>
+        <v>0.013129851282519</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -25190,12 +25128,12 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>TDHOY</t>
+          <t>JPXGY</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>T&amp;D Holdings, Inc.</t>
+          <t>Japan Exchange Group, Inc.</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
@@ -25205,11 +25143,11 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="F25" s="10" t="n">
-        <v>14424766464</v>
+        <v>14020936704</v>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
@@ -25217,21 +25155,19 @@
         </is>
       </c>
       <c r="H25" s="18" t="n">
-        <v>0.6380176864063891</v>
+        <v>0.6395979536579929</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>0.409217877329693</v>
-      </c>
-      <c r="J25" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.3824722514294422</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>-1.916853128246724</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>17.476744</v>
+        <v>37.88889</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>0.008947678009880101</v>
+        <v>0.0406386293465501</v>
       </c>
       <c r="M25" s="20" t="inlineStr">
         <is>
@@ -25243,33 +25179,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="O25" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P25" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="O25" s="19" t="n">
+        <v>72.41255984458697</v>
+      </c>
+      <c r="P25" s="12" t="n">
+        <v>-2.046085497815548</v>
       </c>
       <c r="Q25" s="19" t="n">
-        <v>4.759</v>
+        <v>66.08556879370417</v>
       </c>
       <c r="R25" s="19" t="n">
-        <v>38.21942485376493</v>
+        <v>35.38156234723725</v>
       </c>
       <c r="S25" s="21" t="n">
-        <v>0.6155205882352941</v>
+        <v>0.6566123519161398</v>
       </c>
       <c r="T25" s="15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U25" s="21" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>0.0052923852493239</v>
+        <v>0.0854039464951392</v>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
@@ -25637,7 +25569,7 @@
         </is>
       </c>
       <c r="H30" s="18" t="n">
-        <v>0.5308491037478662</v>
+        <v>0.532987468717646</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>0.470596616659346</v>
@@ -25680,7 +25612,7 @@
         <v>3</v>
       </c>
       <c r="U30" s="21" t="n">
-        <v>0.833</v>
+        <v>0.857</v>
       </c>
       <c r="V30" s="12" t="n">
         <v>0.0197109783402423</v>
@@ -25719,7 +25651,7 @@
         </is>
       </c>
       <c r="H31" s="18" t="n">
-        <v>0.5295633766409822</v>
+        <v>0.524296030474356</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>0.3907990686302594</v>
@@ -25762,7 +25694,7 @@
         <v>1</v>
       </c>
       <c r="U31" s="21" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="V31" s="12" t="n">
         <v>0.0057355918750548</v>
@@ -25975,7 +25907,7 @@
         </is>
       </c>
       <c r="H34" s="18" t="n">
-        <v>0.4850380418059534</v>
+        <v>0.4864676610547675</v>
       </c>
       <c r="I34" s="12" t="n">
         <v>0.3994252121977403</v>
@@ -26018,7 +25950,7 @@
         <v>4</v>
       </c>
       <c r="U34" s="21" t="n">
-        <v>0.857</v>
+        <v>0.875</v>
       </c>
       <c r="V34" s="12" t="n">
         <v>0.0039820636166525</v>
@@ -26143,7 +26075,7 @@
         </is>
       </c>
       <c r="H36" s="18" t="n">
-        <v>0.4551708235446937</v>
+        <v>0.4633644104676809</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>0.45691201158744</v>
@@ -26186,7 +26118,7 @@
         <v>0</v>
       </c>
       <c r="U36" s="21" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="V36" s="12" t="n">
         <v>0.0136389790398918</v>
@@ -26198,26 +26130,26 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>TSIHF</t>
+          <t>TKGSF</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>TSI Holdings Co.,Ltd.</t>
+          <t>Tokyo Gas Co.,Ltd.</t>
         </is>
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="F37" s="10" t="n">
-        <v>553550208</v>
+        <v>13365699584</v>
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
@@ -26225,19 +26157,19 @@
         </is>
       </c>
       <c r="H37" s="18" t="n">
-        <v>0.4451679580704301</v>
+        <v>0.4446449802957746</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>0.3490994068989574</v>
+        <v>0.3403343243210762</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>1.428283314684125</v>
+        <v>2.034479839777741</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>6.5298014</v>
+        <v>9.94074</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>0.0055734012082158</v>
+        <v>0.0077821935868532</v>
       </c>
       <c r="M37" s="20" t="inlineStr">
         <is>
@@ -26250,28 +26182,28 @@
         </is>
       </c>
       <c r="O37" s="19" t="n">
-        <v>3.74040257314795</v>
+        <v>7.21438636457364</v>
       </c>
       <c r="P37" s="12" t="n">
-        <v>1.388657427089533</v>
+        <v>1.786751819397</v>
       </c>
       <c r="Q37" s="19" t="n">
-        <v>7.03893227997725</v>
+        <v>20.188912669164</v>
       </c>
       <c r="R37" s="19" t="n">
-        <v>15.91548806735143</v>
+        <v>20.07506897491193</v>
       </c>
       <c r="S37" s="21" t="n">
-        <v>0.2490592887472759</v>
+        <v>0.7358842593855883</v>
       </c>
       <c r="T37" s="15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U37" s="21" t="n">
         <v>1</v>
       </c>
       <c r="V37" s="12" t="n">
-        <v>0.0033129856540084</v>
+        <v>0.004714949924667</v>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
@@ -26280,26 +26212,26 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>TKGSF</t>
+          <t>TSIHF</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Tokyo Gas Co.,Ltd.</t>
+          <t>TSI Holdings Co.,Ltd.</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="F38" s="10" t="n">
-        <v>13365699584</v>
+        <v>553550208</v>
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
@@ -26307,19 +26239,19 @@
         </is>
       </c>
       <c r="H38" s="18" t="n">
-        <v>0.4446449802957746</v>
+        <v>0.4364391745788531</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>0.3403343243210762</v>
+        <v>0.3490994068989574</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>2.034479839777741</v>
+        <v>1.428283314684125</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>9.94074</v>
+        <v>6.5298014</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>0.0077821935868532</v>
+        <v>0.0055734012082158</v>
       </c>
       <c r="M38" s="20" t="inlineStr">
         <is>
@@ -26332,28 +26264,28 @@
         </is>
       </c>
       <c r="O38" s="19" t="n">
-        <v>7.21438636457364</v>
+        <v>3.74040257314795</v>
       </c>
       <c r="P38" s="12" t="n">
-        <v>1.786751819397</v>
+        <v>1.388657427089533</v>
       </c>
       <c r="Q38" s="19" t="n">
-        <v>20.188912669164</v>
+        <v>7.03893227997725</v>
       </c>
       <c r="R38" s="19" t="n">
-        <v>20.07506897491193</v>
+        <v>15.91548806735143</v>
       </c>
       <c r="S38" s="21" t="n">
-        <v>0.7358842593855883</v>
+        <v>0.2490592887472759</v>
       </c>
       <c r="T38" s="15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U38" s="21" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="V38" s="12" t="n">
-        <v>0.004714949924667</v>
+        <v>0.0033129856540084</v>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
@@ -26475,7 +26407,7 @@
         </is>
       </c>
       <c r="H40" s="18" t="n">
-        <v>0.4101573401799526</v>
+        <v>0.412490994012011</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>0.3538766223035597</v>
@@ -26518,7 +26450,7 @@
         <v>3</v>
       </c>
       <c r="U40" s="21" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="V40" s="12" t="n">
         <v>0.0071119191368184</v>
@@ -26572,7 +26504,7 @@
         <v>0.0258765182914956</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>175.31928752858</v>
+        <v>160.5916782438269</v>
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
@@ -26719,7 +26651,7 @@
         </is>
       </c>
       <c r="H43" s="18" t="n">
-        <v>0.3361824935127728</v>
+        <v>0.3371940757399928</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>0.2964082944268573</v>
@@ -26762,7 +26694,7 @@
         <v>1</v>
       </c>
       <c r="U43" s="21" t="n">
-        <v>0.857</v>
+        <v>0.875</v>
       </c>
       <c r="V43" s="12" t="n">
         <v>0.0029634005366525</v>
@@ -26801,7 +26733,7 @@
         </is>
       </c>
       <c r="H44" s="18" t="n">
-        <v>0.3273201801354208</v>
+        <v>0.3223310559648346</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>0.275206974549108</v>
@@ -26844,7 +26776,7 @@
         <v>3</v>
       </c>
       <c r="U44" s="21" t="n">
-        <v>0.714</v>
+        <v>0.625</v>
       </c>
       <c r="V44" s="12" t="n">
         <v>0.0017813576701523</v>
@@ -26883,7 +26815,7 @@
         </is>
       </c>
       <c r="H45" s="18" t="n">
-        <v>0.3166779468149525</v>
+        <v>0.3106076060174365</v>
       </c>
       <c r="I45" s="12" t="n">
         <v>0.2690467679642238</v>
@@ -26926,7 +26858,7 @@
         <v>2</v>
       </c>
       <c r="U45" s="21" t="n">
-        <v>0.833</v>
+        <v>0.714</v>
       </c>
       <c r="V45" s="12" t="n">
         <v>0.0064787406485281</v>
@@ -26965,7 +26897,7 @@
         </is>
       </c>
       <c r="H46" s="18" t="n">
-        <v>0.2925597367622444</v>
+        <v>0.2943256909076906</v>
       </c>
       <c r="I46" s="12" t="n">
         <v>0.277912225512862</v>
@@ -27008,7 +26940,7 @@
         <v>0</v>
       </c>
       <c r="U46" s="21" t="n">
-        <v>0.714</v>
+        <v>0.75</v>
       </c>
       <c r="V46" s="12" t="n">
         <v>0.0037144205322184</v>
@@ -27296,7 +27228,7 @@
         <v>0.3558647758281111</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.3915895318245857</v>
+        <v>0.3912087549671701</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>0.6643432522078609</v>
@@ -27826,26 +27758,26 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>CEBUF</t>
+          <t>UVRBF</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Cebu Air, Inc.</t>
+          <t>Universal Robina Corporation</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="F22" s="10" t="n">
-        <v>245097648</v>
+        <v>2134621056</v>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
@@ -27853,19 +27785,19 @@
         </is>
       </c>
       <c r="H22" s="18" t="n">
-        <v>0.5135484020532165</v>
+        <v>0.5083049845970807</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>0.3911504729782537</v>
+        <v>0.3984430656856721</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>4.417637887043991</v>
+        <v>0.5704320635594212</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>2.857143</v>
+        <v>12.5</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>0.0130484868078603</v>
+        <v>0.0171762355470315</v>
       </c>
       <c r="M22" s="20" t="inlineStr">
         <is>
@@ -27878,28 +27810,28 @@
         </is>
       </c>
       <c r="O22" s="19" t="n">
-        <v>6.63179481366009</v>
+        <v>13.34475281600089</v>
       </c>
       <c r="P22" s="12" t="n">
-        <v>1.263680797562214</v>
+        <v>0.3105045527589611</v>
       </c>
       <c r="Q22" s="19" t="n">
-        <v>31.53531014145924</v>
+        <v>13.00713026684838</v>
       </c>
       <c r="R22" s="19" t="n">
-        <v>-72.41379359956301</v>
+        <v>-35.98958815017213</v>
       </c>
       <c r="S22" s="21" t="n">
-        <v>0.5581589740683005</v>
+        <v>0.7587261925192698</v>
       </c>
       <c r="T22" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U22" s="21" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>0.0019954370109651</v>
+        <v>0.0120501103444796</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -27908,26 +27840,26 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>UVRBF</t>
+          <t>CEBUF</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Universal Robina Corporation</t>
+          <t>Cebu Air, Inc.</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="F23" s="10" t="n">
-        <v>2134621056</v>
+        <v>245097648</v>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
@@ -27935,19 +27867,19 @@
         </is>
       </c>
       <c r="H23" s="18" t="n">
-        <v>0.5083049845970807</v>
+        <v>0.5065087883841487</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>0.3984430656856721</v>
+        <v>0.3911504729782537</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>0.5704320635594212</v>
+        <v>4.417637887043991</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>12.5</v>
+        <v>2.857143</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>0.0171762355470315</v>
+        <v>0.0130484868078603</v>
       </c>
       <c r="M23" s="20" t="inlineStr">
         <is>
@@ -27960,28 +27892,28 @@
         </is>
       </c>
       <c r="O23" s="19" t="n">
-        <v>13.34475281600089</v>
+        <v>6.63179481366009</v>
       </c>
       <c r="P23" s="12" t="n">
-        <v>0.3105045527589611</v>
+        <v>1.263680797562214</v>
       </c>
       <c r="Q23" s="19" t="n">
-        <v>13.00713026684838</v>
+        <v>31.53531014145924</v>
       </c>
       <c r="R23" s="19" t="n">
-        <v>-35.98958815017213</v>
+        <v>-72.41379359956301</v>
       </c>
       <c r="S23" s="21" t="n">
-        <v>0.7587261925192698</v>
+        <v>0.5581589740683005</v>
       </c>
       <c r="T23" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U23" s="21" t="n">
-        <v>1</v>
+        <v>0.775</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>0.0120501103444796</v>
+        <v>0.0019954370109651</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -28099,7 +28031,7 @@
         </is>
       </c>
       <c r="H25" s="18" t="n">
-        <v>0.4783224254740024</v>
+        <v>0.4797617106058199</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>0.3641178738659836</v>
@@ -28142,7 +28074,7 @@
         <v>3</v>
       </c>
       <c r="U25" s="21" t="n">
-        <v>0.857</v>
+        <v>0.875</v>
       </c>
       <c r="V25" s="12" t="n">
         <v>0.0002537207915702</v>
@@ -28181,7 +28113,7 @@
         </is>
       </c>
       <c r="H26" s="18" t="n">
-        <v>0.4594385079327493</v>
+        <v>0.4608209708452852</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>0.3497426918983646</v>
@@ -28224,7 +28156,7 @@
         <v>2</v>
       </c>
       <c r="U26" s="21" t="n">
-        <v>0.857</v>
+        <v>0.875</v>
       </c>
       <c r="V26" s="12" t="n">
         <v>0.0017389139072165</v>
@@ -28896,26 +28828,26 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>MAEOY</t>
+          <t>RRETY</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Manila Electric Company</t>
+          <t>Robinsons Retail Holdings, Inc.</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="F35" s="10" t="n">
-        <v>10859536384</v>
+        <v>1084450304</v>
       </c>
       <c r="G35" s="17" t="inlineStr">
         <is>
@@ -28923,19 +28855,19 @@
         </is>
       </c>
       <c r="H35" s="18" t="n">
-        <v>0.3277356500272198</v>
+        <v>0.3261115158270656</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>0.291493652891155</v>
+        <v>0.3098009917993615</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>2.07158506891577</v>
+        <v>2.847866991594243</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>12.932886</v>
+        <v>13.157895</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>0.0652832149087739</v>
+        <v>0.0160538806272822</v>
       </c>
       <c r="M35" s="20" t="inlineStr">
         <is>
@@ -28948,28 +28880,28 @@
         </is>
       </c>
       <c r="O35" s="19" t="n">
-        <v>16.71577496338416</v>
+        <v>8.19078175516221</v>
       </c>
       <c r="P35" s="12" t="n">
-        <v>1.373754300299634</v>
+        <v>1.507108577520763</v>
       </c>
       <c r="Q35" s="19" t="n">
-        <v>17.89341789897794</v>
+        <v>9.08317234068523</v>
       </c>
       <c r="R35" s="19" t="n">
-        <v>14.93437054194074</v>
+        <v>70.53353448922891</v>
       </c>
       <c r="S35" s="21" t="n">
-        <v>0.459610668433996</v>
+        <v>0.5437658050533807</v>
       </c>
       <c r="T35" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U35" s="21" t="n">
         <v>1</v>
       </c>
       <c r="V35" s="12" t="n">
-        <v>0.0215641130516111</v>
+        <v>0.0050354559923436</v>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
@@ -28978,26 +28910,26 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>RRETY</t>
+          <t>MAEOY</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Robinsons Retail Holdings, Inc.</t>
+          <t>Manila Electric Company</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="F36" s="10" t="n">
-        <v>1084450304</v>
+        <v>10859536384</v>
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
@@ -29005,19 +28937,19 @@
         </is>
       </c>
       <c r="H36" s="18" t="n">
-        <v>0.3261115158270656</v>
+        <v>0.3216725405017162</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>0.3098009917993615</v>
+        <v>0.291493652891155</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>2.847866991594243</v>
+        <v>2.07158506891577</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>13.157895</v>
+        <v>12.932886</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>0.0160538806272822</v>
+        <v>0.0652832149087739</v>
       </c>
       <c r="M36" s="20" t="inlineStr">
         <is>
@@ -29030,28 +28962,28 @@
         </is>
       </c>
       <c r="O36" s="19" t="n">
-        <v>8.19078175516221</v>
+        <v>16.71577496338416</v>
       </c>
       <c r="P36" s="12" t="n">
-        <v>1.507108577520763</v>
+        <v>1.373754300299634</v>
       </c>
       <c r="Q36" s="19" t="n">
-        <v>9.08317234068523</v>
+        <v>17.89341789897794</v>
       </c>
       <c r="R36" s="19" t="n">
-        <v>70.53353448922891</v>
+        <v>14.93437054194074</v>
       </c>
       <c r="S36" s="21" t="n">
-        <v>0.5437658050533807</v>
+        <v>0.459610668433996</v>
       </c>
       <c r="T36" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U36" s="21" t="n">
-        <v>1</v>
+        <v>0.889</v>
       </c>
       <c r="V36" s="12" t="n">
-        <v>0.0050354559923436</v>
+        <v>0.0215641130516111</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -29919,13 +29851,13 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="13" t="n">
-        <v>0.2887164630275085</v>
+        <v>0.3065329580530889</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.3249844470707819</v>
+        <v>0.342088197787815</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>0.6472407538639148</v>
+        <v>0.6544985162921796</v>
       </c>
     </row>
     <row r="12">
@@ -30145,7 +30077,7 @@
         </is>
       </c>
       <c r="H18" s="18" t="n">
-        <v>0.6472407538639148</v>
+        <v>0.6544985162921796</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>0.4178164264977979</v>
@@ -30190,7 +30122,7 @@
         <v>2</v>
       </c>
       <c r="U18" s="21" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="V18" s="12" t="n">
         <v>0.0519397729257641</v>
@@ -30256,10 +30188,8 @@
       <c r="O19" s="19" t="n">
         <v>-7.97992585224703</v>
       </c>
-      <c r="P19" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P19" s="12" t="n">
+        <v>-0.2433460076045627</v>
       </c>
       <c r="Q19" s="19" t="n">
         <v>259.4327990135635</v>
@@ -30397,10 +30327,10 @@
         </is>
       </c>
       <c r="H21" s="18" t="n">
-        <v>0.1476466393072403</v>
+        <v>0.2088038797471077</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>0.1720512956988361</v>
+        <v>0.2433172758011578</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>-0.94326552737964</v>
@@ -30426,10 +30356,8 @@
       <c r="O21" s="19" t="n">
         <v>115.2434648898001</v>
       </c>
-      <c r="P21" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="P21" s="12" t="n">
+        <v>-0.0398137939483033</v>
       </c>
       <c r="Q21" s="19" t="n">
         <v>0</v>

--- a/top_n_otc.xlsx
+++ b/top_n_otc.xlsx
@@ -574,6 +574,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF1B2430"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1610,6 +1611,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFAD1457"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2086,6 +2088,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF6A1B9A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2556,6 +2559,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFAD4300"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -3028,6 +3032,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF2E7D32"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -3660,6 +3665,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFAD1457"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4132,6 +4138,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF1F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -6840,6 +6847,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFAD4300"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -7310,6 +7318,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF2E7D32"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -8382,6 +8391,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF6A1B9A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -8932,6 +8942,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF6A1B9A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -10670,6 +10681,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF1F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -13490,6 +13502,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF00838F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -13960,6 +13973,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF2E7D32"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -14430,6 +14444,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF2E7D32"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -14904,6 +14919,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF00838F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -15374,6 +15390,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFC77400"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -15850,6 +15867,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFAD1457"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -16326,6 +16344,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF2E7D32"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -16796,6 +16815,7 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFAD4300"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -17268,6 +17288,7 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF00838F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -17738,6 +17759,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFC77400"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -20116,6 +20138,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF6A1B9A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -22950,6 +22973,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFAD1457"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -23586,6 +23610,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFAD1457"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -24148,6 +24173,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF6A1B9A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -27040,6 +27066,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFC77400"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -29666,6 +29693,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF8D6E00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>

--- a/top_n_otc.xlsx
+++ b/top_n_otc.xlsx
@@ -4883,17 +4883,17 @@
       </c>
       <c r="B45" s="21" t="inlineStr">
         <is>
-          <t>SNAVF</t>
+          <t>QCCUF</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>Star Navigation Systems Group Ltd.</t>
+          <t>QC Copper and Gold Inc.</t>
         </is>
       </c>
       <c r="D45" s="27" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="F45" s="20" t="n">
-        <v>25941764</v>
+        <v>56497304</v>
       </c>
       <c r="G45" s="28" t="inlineStr">
         <is>
@@ -4925,42 +4925,46 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L45" s="30" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="L45" s="22" t="n">
+        <v>4.6712804</v>
       </c>
       <c r="M45" s="31" t="n">
-        <v>-14.01304861149766</v>
+        <v>-14.54865342715365</v>
       </c>
       <c r="N45" s="30" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O45" s="31" t="n">
-        <v>137.85267741085</v>
-      </c>
-      <c r="P45" s="22" t="n">
-        <v>-0.0821140455937148</v>
+      <c r="O45" s="30" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="P45" s="30" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q45" s="31" t="n">
-        <v>-5008.380577770196</v>
+        <v>0</v>
       </c>
       <c r="R45" s="31" t="n">
-        <v>64</v>
+        <v>45.16</v>
       </c>
       <c r="S45" s="32" t="n">
-        <v>0.3823529411764705</v>
+        <v>0.2920374900193196</v>
       </c>
       <c r="T45" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U45" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V45" s="22" t="n">
-        <v>260.3052810082381</v>
+        <v>0.333</v>
+      </c>
+      <c r="V45" s="30" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
@@ -4969,17 +4973,17 @@
       </c>
       <c r="B46" s="21" t="inlineStr">
         <is>
-          <t>QCCUF</t>
+          <t>SNAVF</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>QC Copper and Gold Inc.</t>
+          <t>Star Navigation Systems Group Ltd.</t>
         </is>
       </c>
       <c r="D46" s="27" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr">
@@ -4988,7 +4992,7 @@
         </is>
       </c>
       <c r="F46" s="20" t="n">
-        <v>56497304</v>
+        <v>25941764</v>
       </c>
       <c r="G46" s="28" t="inlineStr">
         <is>
@@ -5011,46 +5015,42 @@
           <t>–</t>
         </is>
       </c>
-      <c r="L46" s="22" t="n">
-        <v>4.6712804</v>
+      <c r="L46" s="30" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M46" s="31" t="n">
-        <v>-14.54865342715365</v>
+        <v>-14.01304861149766</v>
       </c>
       <c r="N46" s="30" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O46" s="30" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P46" s="30" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="O46" s="31" t="n">
+        <v>137.85267741085</v>
+      </c>
+      <c r="P46" s="22" t="n">
+        <v>-0.0821140455937148</v>
       </c>
       <c r="Q46" s="31" t="n">
-        <v>0</v>
+        <v>-5008.380577770196</v>
       </c>
       <c r="R46" s="31" t="n">
-        <v>45.16</v>
+        <v>64</v>
       </c>
       <c r="S46" s="32" t="n">
-        <v>0.2920374900193196</v>
+        <v>0.3823529411764705</v>
       </c>
       <c r="T46" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U46" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="V46" s="30" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.5</v>
+      </c>
+      <c r="V46" s="22" t="n">
+        <v>260.3052810082381</v>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
@@ -10911,26 +10911,26 @@
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>SRMMF</t>
+          <t>ADPXY</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>Sarama Resources Ltd</t>
+          <t>Audio Pixels Holdings Limited</t>
         </is>
       </c>
       <c r="D30" s="27" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="F30" s="20" t="n">
-        <v>20212274</v>
+        <v>87630304</v>
       </c>
       <c r="G30" s="28" t="inlineStr">
         <is>
@@ -10959,33 +10959,35 @@
         </is>
       </c>
       <c r="M30" s="31" t="n">
-        <v>-9.258245757008829</v>
+        <v>-7.116439993178609</v>
       </c>
       <c r="N30" s="30" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O30" s="31" t="n">
-        <v>185.3552086215862</v>
+      <c r="O30" s="30" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="P30" s="22" t="n">
-        <v>-0.0402464951569368</v>
+        <v>-2.097316671176232</v>
       </c>
       <c r="Q30" s="31" t="n">
         <v>0</v>
       </c>
       <c r="R30" s="31" t="n">
-        <v>26.67</v>
+        <v>24.79201103390056</v>
       </c>
       <c r="S30" s="32" t="n">
-        <v>0.2767857142857142</v>
+        <v>0.2953856748789265</v>
       </c>
       <c r="T30" s="26" t="n">
         <v>1</v>
       </c>
       <c r="U30" s="32" t="n">
-        <v>0.5</v>
+        <v>0.37</v>
       </c>
       <c r="V30" s="30" t="inlineStr">
         <is>
@@ -10999,26 +11001,26 @@
       </c>
       <c r="B31" s="21" t="inlineStr">
         <is>
-          <t>ADPXY</t>
+          <t>SRMMF</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>Audio Pixels Holdings Limited</t>
+          <t>Sarama Resources Ltd</t>
         </is>
       </c>
       <c r="D31" s="27" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="F31" s="20" t="n">
-        <v>87630304</v>
+        <v>20212274</v>
       </c>
       <c r="G31" s="28" t="inlineStr">
         <is>
@@ -11047,7 +11049,7 @@
         </is>
       </c>
       <c r="M31" s="31" t="n">
-        <v>-7.116439993178609</v>
+        <v>-9.258245757008829</v>
       </c>
       <c r="N31" s="30" t="inlineStr">
         <is>
@@ -11060,22 +11062,22 @@
         </is>
       </c>
       <c r="P31" s="22" t="n">
-        <v>-2.097316671176232</v>
+        <v>-0.0402464951569368</v>
       </c>
       <c r="Q31" s="31" t="n">
         <v>0</v>
       </c>
       <c r="R31" s="31" t="n">
-        <v>24.79201103390056</v>
+        <v>26.67</v>
       </c>
       <c r="S31" s="32" t="n">
-        <v>0.2953856748789265</v>
+        <v>0.2767857142857142</v>
       </c>
       <c r="T31" s="26" t="n">
         <v>1</v>
       </c>
       <c r="U31" s="32" t="n">
-        <v>0.37</v>
+        <v>0.435</v>
       </c>
       <c r="V31" s="30" t="inlineStr">
         <is>
@@ -11284,7 +11286,7 @@
         <v>0.2835127573447395</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>0.2817081730186686</v>
+        <v>0.2816802930961401</v>
       </c>
       <c r="E11" s="24" t="n">
         <v>1.14932350883163</v>
@@ -12257,8 +12259,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="O27" s="31" t="n">
-        <v>214.8679223530429</v>
+      <c r="O27" s="30" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="P27" s="22" t="n">
         <v>-7.475150278954917</v>
@@ -31192,17 +31196,17 @@
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>OPTBF</t>
+          <t>LECBF</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>Oriental Petroleum and Minerals Corporation</t>
+          <t>Lepanto Consolidated Mining Company</t>
         </is>
       </c>
       <c r="D44" s="27" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr">
@@ -31211,7 +31215,7 @@
         </is>
       </c>
       <c r="F44" s="20" t="n">
-        <v>11363033</v>
+        <v>146026672</v>
       </c>
       <c r="G44" s="28" t="inlineStr">
         <is>
@@ -31224,10 +31228,8 @@
       <c r="I44" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="30" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="J44" s="22" t="n">
+        <v>2.265</v>
       </c>
       <c r="K44" s="30" t="inlineStr">
         <is>
@@ -31235,10 +31237,12 @@
         </is>
       </c>
       <c r="L44" s="22" t="n">
-        <v>1.3343387</v>
-      </c>
-      <c r="M44" s="31" t="n">
-        <v>-15.57682706720996</v>
+        <v>1.1974484</v>
+      </c>
+      <c r="M44" s="30" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N44" s="30" t="inlineStr">
         <is>
@@ -31256,22 +31260,26 @@
         </is>
       </c>
       <c r="Q44" s="31" t="n">
-        <v>-251.0291595197256</v>
-      </c>
-      <c r="R44" s="31" t="n">
-        <v>-50</v>
-      </c>
-      <c r="S44" s="32" t="n">
-        <v>0.3161585038519205</v>
+        <v>51.17900399999999</v>
+      </c>
+      <c r="R44" s="30" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="S44" s="34" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="T44" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U44" s="32" t="n">
-        <v>0.3</v>
+        <v>0.667</v>
       </c>
       <c r="V44" s="22" t="n">
-        <v>9.745312</v>
+        <v>0.027595345</v>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
@@ -31280,17 +31288,17 @@
       </c>
       <c r="B45" s="21" t="inlineStr">
         <is>
-          <t>LECBF</t>
+          <t>OPTBF</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>Lepanto Consolidated Mining Company</t>
+          <t>Oriental Petroleum and Minerals Corporation</t>
         </is>
       </c>
       <c r="D45" s="27" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
@@ -31299,7 +31307,7 @@
         </is>
       </c>
       <c r="F45" s="20" t="n">
-        <v>146026672</v>
+        <v>11363033</v>
       </c>
       <c r="G45" s="28" t="inlineStr">
         <is>
@@ -31312,8 +31320,10 @@
       <c r="I45" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J45" s="22" t="n">
-        <v>2.265</v>
+      <c r="J45" s="30" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K45" s="30" t="inlineStr">
         <is>
@@ -31321,12 +31331,10 @@
         </is>
       </c>
       <c r="L45" s="22" t="n">
-        <v>1.1974484</v>
-      </c>
-      <c r="M45" s="30" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.3343387</v>
+      </c>
+      <c r="M45" s="31" t="n">
+        <v>-15.57682706720996</v>
       </c>
       <c r="N45" s="30" t="inlineStr">
         <is>
@@ -31344,26 +31352,22 @@
         </is>
       </c>
       <c r="Q45" s="31" t="n">
-        <v>51.17900399999999</v>
-      </c>
-      <c r="R45" s="30" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="S45" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-251.0291595197256</v>
+      </c>
+      <c r="R45" s="31" t="n">
+        <v>-50</v>
+      </c>
+      <c r="S45" s="32" t="n">
+        <v>0.3161585038519205</v>
       </c>
       <c r="T45" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U45" s="32" t="n">
-        <v>0.667</v>
+        <v>0.3</v>
       </c>
       <c r="V45" s="22" t="n">
-        <v>0.027595345</v>
+        <v>9.745312</v>
       </c>
     </row>
   </sheetData>
